--- a/outputs/evaluation/architecture/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,87 +447,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>all elements (name | isPartOf)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.5227000000000001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.8214</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.7188</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.7662</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>field</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>accuracy</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>mean semantic meaning</t>
-        </is>
+      <c r="B3" t="n">
+        <v>0.7037</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5938</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.7475000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.8846000000000001</v>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>mean semantic meaning</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2308</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.2644</v>
+        <v>0.84</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pageNumber</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8077</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.32</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2961</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>isPartOf</t>
+          <t>pageNumber</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1818</v>
+        <v>0.72</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -538,15 +541,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>isPartOf</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>fixes</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -608,16 +626,16 @@
         <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8636</v>
+        <v>0.7619</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7308</v>
+        <v>0.6153999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -652,16 +670,16 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4</v>
+        <v>0.2353</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2222</v>
+        <v>0.4444</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -717,56 +735,66 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>False Positives</t>
+          <t>Validated correct (name for units/patterns, isPartOf for connectors)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>False Negatives</t>
+          <t>False Positives</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Element Precision</t>
+          <t>False Negatives</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7879</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Element Recall</t>
+          <t>Precision (all elements; units/patterns by name, connectors by isPartOf)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6341</v>
+        <v>0.5227000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Recall (all elements; units/patterns by name, connectors by isPartOf)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Match threshold (cosine)</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -836,22 +864,22 @@
         <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -864,22 +892,22 @@
         <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -892,22 +920,22 @@
         <v>41</v>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -920,22 +948,22 @@
         <v>37</v>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -948,22 +976,22 @@
         <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
         <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -991,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1005,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1113,158 +1141,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M05_AD03</t>
+          <t>CF_M05_AU21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.3863</v>
+        <v>0.3827</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MVVM (Model-View-ViewModel)</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Used in the Angular frontend, this pattern separates the user interface (View) from the logic and data processing (ViewModel) and the data contract (Model).</t>
+          <t>Handles database access and queries.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['P_03']</t>
+          <t>['AU_14']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Data access layer (Repositories)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>the Repositories are responsible for performing queries on the database.</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>CF_M05_AD04</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>CF_M05_AU21</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CF_M05_AD03</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MVVM (Model-View-ViewModel)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Used in the Angular frontend, this pattern separates the user interface (View) from the logic and data processing (ViewModel) and the data contract (Model).</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>['P_03']</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>MVVM</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">Angular applies the MVVM pattern (Model-View-ViewModel), since its architecture is
 based on components and services. </t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="P3" t="n">
         <v>62</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>CF_M05_AD03</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CF_M05_AU07</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0.4618</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Amazon Web Services</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Cloud provider hosting the system infrastructure.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>60, 81</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Amazon EKS</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
-which allows the use of Kubernetes (K8s), a container orchestration platform created by
-Google, without the need to install or maintain it. </t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>CF_M05_AD05</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M05_AU07</t>
+          <t>CF_M05_AD03</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1272,12 +1302,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M05_AU20</t>
+          <t>CF_M05_AU15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1286,64 +1316,69 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5857</v>
+        <v>0.5447</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Contract Layer</t>
+          <t>Model (Backend)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Layer containing DTOs and Mappers for API communication.</t>
+          <t>Represents internal persistent data entities.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>68, 73</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>['AU_14']</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Contract Layer (DTO/Mappers)</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
-request to be structured, providing a customized format based on response requirements.</t>
+          <t>Models are the TypeScript classes that define the data contract consumed by the
+view and the ViewModel. These classes allow the View to know what data to display and
+the ViewModel to know how to manipulate it</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
+          <t>CF_M05_AD03</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M05_AU20</t>
+          <t>CF_M05_AU15</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1351,12 +1386,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M05_AU01</t>
+          <t>CF_M05_AU06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1365,127 +1400,374 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6157</v>
+        <v>0.5586</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Model (Frontend)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Central routing service that manages traffic and communications between external services and internal microservices.</t>
+          <t>TypeScript classes defining the data contract for the frontend.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>57, 60</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>['AU_10']</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>The client, also called the frontEnd, is responsible for the presentation and user experience
+of the application by encapsulating the interface logic and coordinating the calls to the server
+API.</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CF_M05_AD02</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>CF_M05_AU06</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5783</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Presentation Layer (Frontend)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Handles user interface and interaction, implemented as a Single-Page Application.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>61, 62</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Presentation Layer (Controllers)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>The controllers, through specific
+functions, process the requests received, manage the validation of the information and channel
+the requests to the corresponding modules or services of the data layer.</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CF_M05_AD04</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CF_M05_AU37</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5809</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Service (Backend)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Implements business logic and processes data.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>['AU_14']</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
+responsibilities are separated:</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CF_M05_AD02</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>CF_M05_AU37</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7024</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Leader Service</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Central routing service that manages traffic and security between external requests and internal microservices.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>57, 60</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>Leader Microservice</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>This microservice has as its main function the routing of all communications to the corresponding microservice
 within the system architecture. It acts as a central point for traffic management, ensuring that any interaction,
 both with external services and between internal microservices, is carried out in an orderly and secure manner.</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="P8" t="n">
         <v>57</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>CF_M05_AD01</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
         <is>
           <t>CF_M05_AU01</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="T8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>0.6616</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="D9" t="n">
+        <v>0.7395</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Portal Service</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Centralized interface for accessing applications and hosting frontend binaries.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Centralized interface for accessing VWGS applications, also hosting frontend binaries.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>57, 60</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Portal Microservice</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">The portal microservice's main function is to provide a centralized interface for accessing the different VWGS
 applications. This component acts as an entry point for users, providing a unified experience. In addition to its
@@ -1493,260 +1775,18 @@
 itself and the rest of the portal's applications. </t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="P9" t="n">
         <v>57</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>CF_M05_AD01</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>CF_M05_AU02</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU19</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.7126</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Domain Layer</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Layer defining internal data models.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>68, 71</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Domain Layer (Models)</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Models represent the internal and persistent structure of the system entities, reflecting the
-stored information identically.</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>CF_M05_AD04</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU19</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.7278</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Presentation Layer</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Frontend layer handling user interface and interactions.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>61, 68</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Presentation Layer (Controllers)</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>The controllers, through specific
-functions, process the requests received, manage the validation of the information and channel
-the requests to the corresponding modules or services of the data layer.</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>CF_M05_AD04</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CF_M05_AU32</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.7332</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>REST API</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Communication protocol used between client and server.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>61, 69</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>['AU_13']</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
-structure and normalize communication with the data layer. </t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
+          <t>CF_M05_AU02</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1768,11 +1808,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7865</v>
+        <v>0.8208</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Scheduler</t>
+          <t>Scheduler Service</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1782,12 +1822,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Service for planning and automating system tasks and maintenance.</t>
+          <t>Handles planning and automation of system tasks.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>59, 60</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1837,12 +1877,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1851,11 +1891,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7957</v>
+        <v>0.8265</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>Communication Log Service</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1865,7 +1905,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Service responsible for user authentication, authorization, and role management.</t>
+          <t>Records and audits all system communications and provides analytics.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1877,13 +1917,13 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Access Control Microservice</t>
+          <t>Communication Log Microservice</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1892,163 +1932,6 @@
         </is>
       </c>
       <c r="O11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The main objective of the Access Control microservice is to manage user authentication and
-permissions within the application. </t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>CF_M05_AD01</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>CF_M05_AU03</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU21</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.8092</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Access Layer</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Repository layer interacting with the database.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>68, 74</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Data access layer (Repositories)</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>the Repositories are responsible for performing queries on the database.</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>CF_M05_AD04</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU21</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CF_M05_AU04</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.8198</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Communication Log</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Service that records all system communications for traceability and auditing.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Communication Log Microservice</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
         <is>
           <t>The main purpose of the Communication Log microservice is to record all
 communications that occur within the system, both between microservices and with external
@@ -2058,655 +1941,163 @@
 and faster analysis.</t>
         </is>
       </c>
-      <c r="P13" t="n">
+      <c r="P11" t="n">
         <v>58.59</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>CF_M05_AD01</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CF_M05_AU18</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="T11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Business Logic Layer</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Service layer implementing domain rules and processing.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>68, 70</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Business Logic Layer (Services)</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Services provide the interface and implementation of all the application's business logic.</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="D12" t="n">
+        <v>0.8353</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Access Control Service</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Manages user authentication, roles, and permissions.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>58, 60</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Access Control Microservice</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The main objective of the Access Control microservice is to manage user authentication and
+permissions within the application. </t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CF_M05_AD01</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU03</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P_05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>CF_M05_AD04</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>CF_M05_AU18</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CF_M05_AU34</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Angular</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Frontend framework used for building the SPA.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>61, 76</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>['AU_15']</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Angular</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>In the present project, the client has been developed with Angular</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>CF_M05_AU06</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>CF_M05_AU34</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CF_M05_AU15</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Frontend component defining data contracts.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>['AU_15']</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Models are the TypeScript classes that define the data contract consumed by the
-view and the ViewModel. These classes allow the View to know what data to display and
-the ViewModel to know how to manipulate it</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>CF_M05_AD03</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>CF_M05_AU15</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>CF_M05_AU14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ViewModel</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Frontend component managing behavior, data processing, and service orchestration.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>['AU_15']</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>ViewModel</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>The ViewModel component groups the TS files of the components and the services they
-have associated with them. Each TS file defines the behavior of the application component
-to which it corresponds, taking care of data processing and validations</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>64</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>CF_M05_AD03</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>CF_M05_AU14</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CF_M05_AU10</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Amazon RDS</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Managed relational database service used for data persistence.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Amazon RDS</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
-microservice and client. </t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>CF_M05_AD05</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>CF_M05_AU10</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AU_12</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CF_M05_AU23</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Connection between Portal Gateway and Leader.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>['AU_03', 'AU_02']</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>AU_12</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>portal, leader</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">It can be observed that leader microservice communicates with Portal microservice. </t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>CF_M05_AU01, CF_M05_AU02</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>CF_M05_AU23</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CF_M05_AU24</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Connection between Leader and internal microservices.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>['AU_02', 'AU_04']</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>leader, access control</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">It can be observed that leader microservice communicates with Access Control microservice. </t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>CF_M05_AU01, CF_M05_AU03</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>CF_M05_AU24</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>leader microservice, access control microservice</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Layered Architecture</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>The server (backend) organizes code into layers to separate responsibilities: presentation, business logic, data access, domain, and contract layers.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>['P_03']</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CF_M05_AD04</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>Layered Architecture</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>The server (backend) organizes code into layers to separate responsibilities: presentation, business logic, data access, domain, and contract layers.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>['P_03']</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Layered Architecture</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Layered architecture is used: Spring Boot organizes the code following the pattern of layers with which
 responsibilities are separated: the presentation layer receives requests and constructs responses, the
@@ -2714,19 +2105,670 @@
 separates the internal model from the external representation of the API.</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>68-69</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>CF_M05_AD04</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CF_M05_AD05</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Cloud Architecture</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>The application is designed, deployed, and executed using cloud computing services (AWS) instead of local or physical servers, allowing for scalability, availability, and accessibility.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Cloud Architecture</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The application applies a cloud architecture . That is, the application is designed,
+deployed and executed using cloud services (cloud computing) instead of local or physical servers.</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>CF_M05_AD05</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CF_M05_AU34</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Angular</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Frontend framework used for the client-side application.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>61, 76</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>['AU_10']</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Angular</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>In the present project, the client has been developed with Angular</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CF_M05_AU06</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>CF_M05_AU34</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CF_M05_AU14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ViewModel</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>TypeScript files and services that process data and orchestrate HTTP calls.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>['AU_10']</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ViewModel</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>The ViewModel component groups the TS files of the components and the services they
+have associated with them. Each TS file defines the behavior of the application component
+to which it corresponds, taking care of data processing and validations</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CF_M05_AD03</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>CF_M05_AU14</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CF_M05_AU13</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HTML and SCSS files responsible for screen presentation and capturing user input.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>['AU_10']</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
+each component that makes up the application. They are responsible for presenting the
+screens and capturing user interactions such as clicks or text entries.</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>CF_M05_AD03</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>CF_M05_AU13</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CF_M05_AU23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>The Portal Service communicates with the Leader Service for traffic routing and security.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>['AU_03', 'AU_02']</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>portal service, leader service</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It can be observed that leader microservice communicates with Portal microservice. </t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CF_M05_AU01, CF_M05_AU02</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>CF_M05_AU23</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>leader microservice, portal microservice</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>The Leader Service communicates with the Scheduler Service.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>56, 59</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>['AU_02', 'AU_06']</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>leader service, scheduler service</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leader microservice communicates with Scheduler microservice. </t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CF_M05_AU01, CF_M05_AU05</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>leader microservice, scheduler microservice</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CF_M05_AU24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>The Leader Service communicates with the Access Control Service.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>56, 58</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>['AU_02', 'AU_04']</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>leader service, access control service</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It can be observed that leader microservice communicates with Access Control microservice. </t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>CF_M05_AU01, CF_M05_AU03</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>CF_M05_AU24</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>leader microservice, access control microservice</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AU_33</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>The ViewModel component communicates with the Model (Frontend) component.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>64, 66</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>['AU_12', 'AU_13']</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>AU_33</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>viewmodel, model (frontend)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CF_M05_AU14, CF_M05_AU15</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>viewmodel, model</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2811,12 +2853,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_AD01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2829,7 +2871,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cloud Architecture</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2839,25 +2881,25 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>The application is designed, deployed, and executed using cloud computing services (AWS) instead of local or physical servers, allowing for scalability, availability, and accessibility.</t>
+          <t>The system is divided into small, independent, and autonomous services where each microservice is responsible for a specific functionality and communicates with others via messaging systems.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>9, 56</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Cloud Architecture</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2867,18 +2909,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The application applies a cloud architecture . That is, the application is designed,
-deployed and executed using cloud services (cloud computing) instead of local or physical servers.</t>
+          <t>Application has an architecture based on microservices.</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_AD01</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2886,17 +2927,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M05_AD01</t>
+          <t>CF_M05_AU33</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2904,55 +2945,65 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Spring Boot</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>The system is divided into small, independent, and autonomous services where each microservice is responsible for a specific functionality and communicates with others via messaging systems.</t>
+          <t>Backend framework used for the server-side application.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9, 56</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>61, 76</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>['AU_14']</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Spring Boot</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Application has an architecture based on microservices.</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+          <t>Spring Boot is used, which provides a platform for exposing a REST API</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>61, 62</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CF_M05_AU37</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CF_M05_AD01</t>
+          <t>CF_M05_AU33</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2960,12 +3011,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M05_AU35</t>
+          <t>CF_M05_AU10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2978,7 +3029,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Amazon RDS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2988,29 +3039,29 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Protocol for message exchange.</t>
+          <t>Managed database service for data persistence.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['AU_13']</t>
+          <t>['AU_07']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Amazon RDS</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3020,18 +3071,22 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>The message
-exchange protocol used in this case is HTTP</t>
+          <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
+microservice and client. </t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CF_M05_AD05</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
-          <t>CF_M05_AU35</t>
+          <t>CF_M05_AU10</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3039,12 +3094,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M05_AU33</t>
+          <t>CF_M05_AU07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3057,7 +3112,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spring Boot</t>
+          <t>Amazon EKS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3067,29 +3122,29 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Backend framework for building microservices.</t>
+          <t>Managed Kubernetes service for container orchestration.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>61, 76</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['AU_16']</t>
+          <t>['AU_07']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Spring Boot</t>
+          <t>Amazon EKS</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3099,110 +3154,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Spring Boot is used, which provides a platform for exposing a REST API</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>61, 62</t>
-        </is>
+          <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
+which allows the use of Kubernetes (K8s), a container orchestration platform created by
+Google, without the need to install or maintain it. </t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>81</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CF_M05_AU37</t>
+          <t>CF_M05_AD05</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CF_M05_AU33</t>
+          <t>CF_M05_AU07</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>CF_M05_AU13</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Frontend component responsible for display and user input capture.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>['AU_15']</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
-each component that makes up the application. They are responsible for presenting the
-screens and capturing user interactions such as clicks or text entries.</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>CF_M05_AD03</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>CF_M05_AU13</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3215,7 +3186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3279,7 +3250,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The end user of the system, including business users, support staff, and administrators.</t>
+          <t>The end user of the portal and applications.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3293,215 +3264,635 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.0433</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>user, internet</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Connection between User and Internet.</t>
+          <t>Cloud provider hosting the system infrastructure.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M05_AU28</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>CF_M05_AU10</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>0.2166</v>
+        <v>0.3794</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Server Layer (Backend)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Network medium for user access.</t>
+          <t>Handles business logic, security, and data persistence.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M05_AU28</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>CF_M05_AU37</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>0.1109</v>
+        <v>0.3573</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>internet, portal</t>
-        </is>
-      </c>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Controller</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Connection between Internet and Portal Gateway.</t>
+          <t>Handles REST API requests and responses.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M05_AU02</t>
+          <t>CF_M05_AU17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Portal Microservice</t>
+          <t>Presentation Layer (Controllers)</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.2336</v>
+        <v>0.4133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>access control, amazon rds</t>
-        </is>
-      </c>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DTO / Mapper</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Connection between internal microservices and Amazon RDS.</t>
+          <t>Handles data transfer objects and conversion between models and external representations.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M05_AU10</t>
+          <t>CF_M05_AU20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Amazon RDS</t>
+          <t>Contract Layer (DTO/Mappers)</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.5413</v>
+        <v>0.2503</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>user, portal service</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data format for communication.</t>
+          <t>The User communicates with the Portal Service via the internet.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M05_AU08</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SonarQube</t>
-        </is>
-      </c>
+          <t>CF_M05_AU27</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.0604</v>
+        <v>0.3682</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>AU_26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>leader service, communication log service</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>The Leader Service communicates with the Communication Log Service.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU25</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0.6552</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>leader service, portal service</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>The Leader Service communicates with the Portal Service.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0.5642</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AU_28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>scheduler service, amazon rds</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>The Scheduler Service communicates with Amazon RDS for data persistence.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4667</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AU_29</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>access control service, amazon rds</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>The Access Control Service communicates with Amazon RDS for data persistence.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU03</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Access Control Microservice</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4402</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>communication log service, amazon rds</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>The Communication Log Service communicates with Amazon RDS for data persistence.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU04</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Communication Log Microservice</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5246</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>portal service, amazon rds</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>The Portal Service communicates with Amazon RDS for data persistence.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4757</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>presentation layer (frontend), viewmodel</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>The Presentation Layer communicates with the ViewModel component.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Presentation Layer (Controllers)</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4574</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AU_34</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>viewmodel, controller</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>The ViewModel component sends HTTP requests to the Controller component.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0.3278</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AU_35</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>controller, service (backend)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>The Controller component communicates with the Service (Backend) component.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CF_M05_AU37</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2506</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AU_36</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>service (backend), repository</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>The Service (Backend) component communicates with the Repository component.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CF_M05_AU37</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2506</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AU_37</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>repository, model (backend)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>The Repository component communicates with the Model (Backend) component.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CF_M05_AU15</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2469</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AU_38</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>service (backend), dto / mapper</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>The Service (Backend) component communicates with the DTO / Mapper component.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CF_M05_AU25</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0.2349</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>P_06</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Design Pattern</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Single-Page Application (SPA)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
         <is>
           <t>The client is developed as a Single-Page Application that renders dynamic views and manages internal navigation without reloading the page.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Communication Log Microservice</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>0.1552</v>
+      <c r="H20" t="n">
+        <v>0.1559</v>
       </c>
     </row>
   </sheetData>
@@ -3515,7 +3906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3563,59 +3954,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_AU06</t>
+          <t>CF_M05_AU08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>SonarQube</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>The client, also called the frontEnd, is responsible for the presentation and user experience
-of the application by encapsulating the interface logic and coordinating the calls to the server
-API.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0296</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CF_M05_AU08</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SonarQube</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
         <is>
           <t>SonarQube is a
 web application that statically analyses the code and offers recommendations and statistics
@@ -3623,60 +3976,93 @@
 problems, the amount of code covered in the tests, code duplication and code smells.</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CF_M05_AU09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Grafana</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.0604</v>
+        <v>0.0195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AU09</t>
+          <t>CF_M05_AU11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Grafana</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
+          <t>These two microservices are responsible for
+calls to external services related to car sales.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Spring Boot</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.2069</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AU11</t>
+          <t>CF_M05_AU12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3686,7 +4072,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>GSB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -3698,169 +4084,166 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spring Boot</t>
+          <t>User</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.2108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AU12</t>
+          <t>CF_M05_AU16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GSB</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
-        <is>
-          <t>These two microservices are responsible for
-calls to external services related to car sales.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU16</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0.0968</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CF_M05_AU18</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Business Logic Layer (Services)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Services provide the interface and implementation of all the application's business logic.</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Data Access Layer</t>
+          <t>Server Layer (Backend)</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.2117</v>
+        <v>0.1622</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M05_AU22</t>
+          <t>CF_M05_AU19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>leader microservice, scheduler microservice</t>
-        </is>
-      </c>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Domain Layer (Models)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leader microservice communicates with Scheduler microservice. </t>
+          <t>Models represent the internal and persistent structure of the system entities, reflecting the
+stored information identically.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>MVVM (Model-View-ViewModel)</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.5749</v>
+        <v>0.1898</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M05_AU25</t>
+          <t>CF_M05_AU20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>leader microservice, access control microservice</t>
-        </is>
-      </c>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Contract Layer (DTO/Mappers)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">It can be observed that leader microservice communicates with Communication Log microservice. </t>
+          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
+request to be structured, providing a customized format based on response requirements.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Communication Log</t>
+          <t>DTO / Mapper</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.592</v>
+        <v>0.2503</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M05_AU27</t>
+          <t>CF_M05_AU25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3871,32 +4254,28 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>portal microservice, presentation layer (controllers)</t>
+          <t>leader microservice, access control microservice</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Portal microservice communicates with the frontend indirectly through the Leader microservice</t>
+          <t xml:space="preserve">It can be observed that leader microservice communicates with Communication Log microservice. </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
+          <t>AU_26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0.4374</v>
+        <v>0.6552</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M05_AU28</t>
+          <t>CF_M05_AU27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3907,32 +4286,28 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>viewmodel, view</t>
+          <t>portal microservice, presentation layer (controllers)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+          <t>Portal microservice communicates with the frontend indirectly through the Leader microservice</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ViewModel</t>
-        </is>
-      </c>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5286</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M05_AU29</t>
+          <t>CF_M05_AU28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3943,7 +4318,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>viewmodel, model</t>
+          <t>viewmodel, view</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3953,7 +4328,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3962,7 +4337,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.4976</v>
       </c>
     </row>
     <row r="13">
@@ -3987,16 +4362,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Access Control</t>
-        </is>
-      </c>
+          <t>AU_34</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1174</v>
+        <v>0.3278</v>
       </c>
     </row>
     <row r="14">
@@ -4019,87 +4390,120 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Data Access Layer</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.0654</v>
+        <v>0.2747</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CF_M05_AU37</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
-responsibilities are separated:</t>
+          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
+structure and normalize communication with the data layer. </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
       <c r="H15" t="n">
-        <v>0.0133</v>
+        <v>0.0446</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CF_M05_AD06</t>
+          <t>CF_M05_AU35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Shared Database</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
+        <is>
+          <t>The message
+exchange protocol used in this case is HTTP</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>AU_34</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0.2704</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Shared Database</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Data Access Layer</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>0.1518</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0.0687</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.6579</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.6098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7037</v>
+        <v>0.875</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5938</v>
+        <v>0.6562</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.8131</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.84</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.32</v>
+        <v>0.3846</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2961</v>
+        <v>0.2829</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.72</v>
+        <v>0.7692</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.25</v>
+        <v>0.6667</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -626,16 +626,16 @@
         <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7619</v>
+        <v>0.9444</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6538</v>
       </c>
     </row>
     <row r="3">
@@ -670,13 +670,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2353</v>
+        <v>0.2857</v>
       </c>
       <c r="F4" t="n">
         <v>0.4444</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.6579</v>
       </c>
     </row>
     <row r="9">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.6098</v>
       </c>
     </row>
     <row r="10">
@@ -864,22 +864,22 @@
         <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G2" t="n">
         <v>21</v>
       </c>
-      <c r="E2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G2" t="n">
-        <v>19</v>
-      </c>
       <c r="H2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -892,22 +892,22 @@
         <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -920,22 +920,22 @@
         <v>41</v>
       </c>
       <c r="C4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -948,22 +948,22 @@
         <v>37</v>
       </c>
       <c r="C5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
+        <v>26</v>
+      </c>
+      <c r="F5" t="n">
         <v>25</v>
       </c>
-      <c r="F5" t="n">
-        <v>24</v>
-      </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -976,22 +976,22 @@
         <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -1019,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:T27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,81 +1141,78 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M05_AU21</t>
+          <t>CF_M05_P03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.3827</v>
+        <v>0.3929</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>MVVM (Model-View-ViewModel)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Handles database access and queries.</t>
+          <t>Used in the Angular frontend, this pattern separates the user interface (View) from the logic and data processing (ViewModel) and the data contract (Model).</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['AU_14']</t>
+          <t>['P_03']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Data access layer (Repositories)</t>
+          <t>MVVM</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>the Repositories are responsible for performing queries on the database.</t>
+          <t xml:space="preserve">Angular applies the MVVM pattern (Model-View-ViewModel), since its architecture is
+based on components and services. </t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>CF_M05_AD04</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M05_AU21</t>
+          <t>CF_M05_P03</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -1223,78 +1220,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M05_AD03</t>
+          <t>CF_M05_AU07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.395</v>
+        <v>0.4209</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MVVM (Model-View-ViewModel)</t>
+          <t>Amazon Web Services</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Used in the Angular frontend, this pattern separates the user interface (View) from the logic and data processing (ViewModel) and the data contract (Model).</t>
+          <t>Cloud provider hosting the system infrastructure.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>['P_03']</t>
-        </is>
-      </c>
+          <t>60, 81</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>MVVM</t>
+          <t>Amazon EKS</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Angular applies the MVVM pattern (Model-View-ViewModel), since its architecture is
-based on components and services. </t>
+          <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
+which allows the use of Kubernetes (K8s), a container orchestration platform created by
+Google, without the need to install or maintain it. </t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>CF_M05_P05</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M05_AD03</t>
+          <t>CF_M05_AU07</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1302,12 +1300,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M05_AU15</t>
+          <t>CF_M05_AU01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1316,69 +1314,65 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5447</v>
+        <v>0.7083</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Model (Backend)</t>
+          <t>Leader Service</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Represents internal persistent data entities.</t>
+          <t>Microservice responsible for routing communications to the appropriate microservice and managing traffic.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>['AU_14']</t>
-        </is>
-      </c>
+          <t>57, 60</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Leader Microservice</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Models are the TypeScript classes that define the data contract consumed by the
-view and the ViewModel. These classes allow the View to know what data to display and
-the ViewModel to know how to manipulate it</t>
+          <t>This microservice has as its main function the routing of all communications to the corresponding microservice
+within the system architecture. It acts as a central point for traffic management, ensuring that any interaction,
+both with external services and between internal microservices, is carried out in an orderly and secure manner.</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>CF_M05_AD03</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M05_AU15</t>
+          <t>CF_M05_AU01</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1386,12 +1380,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M05_AU06</t>
+          <t>CF_M05_AU21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1400,69 +1394,63 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5586</v>
+        <v>0.7496</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Model (Frontend)</t>
+          <t>Data Access Layer (Repository)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TypeScript classes defining the data contract for the frontend.</t>
+          <t>Backend layer interacting with the database.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>['AU_10']</t>
-        </is>
-      </c>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Data access layer (Repositories)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>The client, also called the frontEnd, is responsible for the presentation and user experience
-of the application by encapsulating the interface logic and coordinating the calls to the server
-API.</t>
+          <t>the Repositories are responsible for performing queries on the database.</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CF_M05_AD02</t>
+          <t>CF_M05_P04</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M05_AU06</t>
+          <t>CF_M05_AU21</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1470,12 +1458,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M05_AU17</t>
+          <t>CF_M05_AU02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1484,290 +1472,47 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5783</v>
+        <v>0.7496</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Presentation Layer (Frontend)</t>
+          <t>Portal Service</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Handles user interface and interaction, implemented as a Single-Page Application.</t>
+          <t>Microservice providing a centralized interface for accessing applications and hosting frontend binaries.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>61, 62</t>
+          <t>57, 60</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Presentation Layer (Controllers)</t>
+          <t>Portal Microservice</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
-        <is>
-          <t>The controllers, through specific
-functions, process the requests received, manage the validation of the information and channel
-the requests to the corresponding modules or services of the data layer.</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>CF_M05_AD04</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU37</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.5809</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Service (Backend)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Implements business logic and processes data.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>['AU_14']</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
-responsibilities are separated:</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>CF_M05_AD02</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU37</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AU_02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CF_M05_AU01</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.7024</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Leader Service</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Central routing service that manages traffic and security between external requests and internal microservices.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>57, 60</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>AU_02</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Leader Microservice</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>This microservice has as its main function the routing of all communications to the corresponding microservice
-within the system architecture. It acts as a central point for traffic management, ensuring that any interaction,
-both with external services and between internal microservices, is carried out in an orderly and secure manner.</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>CF_M05_AD01</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>CF_M05_AU01</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AU_03</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CF_M05_AU02</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.7395</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Portal Service</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Centralized interface for accessing VWGS applications, also hosting frontend binaries.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>57, 60</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>AU_03</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Portal Microservice</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">The portal microservice's main function is to provide a centralized interface for accessing the different VWGS
 applications. This component acts as an entry point for users, providing a unified experience. In addition to its
@@ -1775,80 +1520,159 @@
 itself and the rest of the portal's applications. </t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="P6" t="n">
         <v>57</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>CF_M05_AD01</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CF_M05_P01</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="T6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CF_M05_AU19</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7706</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Domain Layer (Model)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Backend layer defining internal data entities.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Domain Layer (Models)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Models represent the internal and persistent structure of the system entities, reflecting the
+stored information identically.</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>CF_M05_AU19</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>CF_M05_AU05</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>0.8208</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D8" t="n">
+        <v>0.8219</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Scheduler Service</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Handles planning and automation of system tasks.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>59, 60</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Microservice for planning and executing automated system tasks.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Scheduler Microservice</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Its main function is the
 planning and scheduling of processes within the system. This component allows you to define,
@@ -1858,18 +1682,175 @@
 microservices.</t>
         </is>
       </c>
+      <c r="P8" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CF_M05_P01</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU05</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU18</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8252</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Business Logic Layer (Service)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Backend layer implementing business rules.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Business Logic Layer (Services)</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Services provide the interface and implementation of all the application's business logic.</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU18</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8282</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Access Control Service</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Microservice responsible for user authentication and permission management.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>58, 60</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Access Control Microservice</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The main objective of the Access Control microservice is to manage user authentication and
+permissions within the application. </t>
+        </is>
+      </c>
       <c r="P10" t="n">
-        <v>59.6</v>
+        <v>58</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CF_M05_AD01</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M05_AU05</t>
+          <t>CF_M05_AU03</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1891,7 +1872,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.8265</v>
+        <v>0.8347</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1905,12 +1886,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Records and audits all system communications and provides analytics.</t>
+          <t>Microservice for logging system communications and providing audit/statistical data.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>58, 60</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1946,7 +1927,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CF_M05_AD01</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -1960,12 +1941,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1974,64 +1955,64 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.8353</v>
+        <v>0.8541</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Access Control Service</t>
+          <t>Contract Layer (DTO/Mapper)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Manages user authentication, roles, and permissions.</t>
+          <t>Backend layer separating internal models from external API representations.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>58, 60</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Access Control Microservice</t>
+          <t>Contract Layer (DTO/Mappers)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">The main objective of the Access Control microservice is to manage user authentication and
-permissions within the application. </t>
+          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
+request to be structured, providing a customized format based on response requirements.</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CF_M05_AD01</t>
+          <t>CF_M05_P04</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU20</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2039,35 +2020,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
+          <t>CF_M05_AU17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0.8556</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Layered Architecture</t>
+          <t>Presentation Layer (Controller)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>The server (backend) organizes code into layers to separate responsibilities: presentation, business logic, data access, domain, and contract layers.</t>
+          <t>Backend layer handling REST requests and responses.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2075,29 +2056,109 @@
           <t>68</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>['P_03']</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
+          <t>Presentation Layer (Controllers)</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>The controllers, through specific
+functions, process the requests received, manage the validation of the information and channel
+the requests to the corresponding modules or services of the data layer.</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P_05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>Layered Architecture</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>The server (backend) organizes code into layers to separate responsibilities: presentation, business logic, data access, domain, and contract layers.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>['P_03']</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>P_05</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Layered Architecture</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Layered architecture is used: Spring Boot organizes the code following the pattern of layers with which
 responsibilities are separated: the presentation layer receives requests and constructs responses, the
@@ -2105,91 +2166,16 @@
 separates the internal model from the external representation of the API.</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>68-69</t>
         </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>CF_M05_AD04</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CF_M05_AD05</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Cloud Architecture</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>The application is designed, deployed, and executed using cloud computing services (AWS) instead of local or physical servers, allowing for scalability, availability, and accessibility.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Cloud Architecture</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> The application applies a cloud architecture . That is, the application is designed,
-deployed and executed using cloud services (cloud computing) instead of local or physical servers.</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>60</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_P04</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2197,12 +2183,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M05_AU34</t>
+          <t>CF_M05_AU15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2215,63 +2201,61 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Angular</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Frontend framework used for the client-side application.</t>
+          <t>Frontend component defining data contracts.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>61, 76</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>['AU_10']</t>
-        </is>
-      </c>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Angular</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>In the present project, the client has been developed with Angular</t>
+          <t>Models are the TypeScript classes that define the data contract consumed by the
+view and the ViewModel. These classes allow the View to know what data to display and
+the ViewModel to know how to manipulate it</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CF_M05_AU06</t>
+          <t>CF_M05_P03</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M05_AU34</t>
+          <t>CF_M05_AU15</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2279,12 +2263,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M05_AU14</t>
+          <t>CF_M05_AU34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2297,883 +2281,936 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ViewModel</t>
+          <t>Angular</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>TypeScript files and services that process data and orchestrate HTTP calls.</t>
+          <t>Frontend framework used for building the SPA.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>['AU_10']</t>
-        </is>
-      </c>
+          <t>61, 76</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
+          <t>Angular</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>In the present project, the client has been developed with Angular</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CF_M05_AU06</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>CF_M05_AU34</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CF_M05_AU10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Database engine used for data persistence.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
+microservice and client. </t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>CF_M05_P05</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>CF_M05_AU10</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>The Leader Service routes communications to the Scheduler Service.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>57, 60</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>['AU_02', 'AU_06']</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>leader service, scheduler service</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leader microservice communicates with Scheduler microservice. </t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CF_M05_AU01, CF_M05_AU05</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>leader microservice, scheduler microservice</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CF_M05_AU24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>The Leader Service routes communications to the Access Control Service.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>57, 60</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>['AU_02', 'AU_04']</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>leader service, access control service</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It can be observed that leader microservice communicates with Access Control microservice. </t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CF_M05_AU01, CF_M05_AU03</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>CF_M05_AU24</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>leader microservice, access control microservice</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CF_M05_AU23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>The Leader Service routes communications to the Portal Service.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>57, 60</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>['AU_02', 'AU_03']</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>leader service, portal service</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It can be observed that leader microservice communicates with Portal microservice. </t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>CF_M05_AU01, CF_M05_AU02</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>CF_M05_AU23</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>leader microservice, portal microservice</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AU_28</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CF_M05_AU28</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>The View component captures user interactions and sends them to the ViewModel.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>62, 64</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>['AU_11', 'AU_12']</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>AU_28</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>view, viewmodel</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CF_M05_AU14, CF_M05_AU13</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>CF_M05_AU28</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>viewmodel, view</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>The application organizes code into two distinct components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>The application follows the Client-Server pattern which organizes the code into two distinct
+components: the client, which makes service requests, and the server, which receives,
+processes, and returns responses.</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Classification Changed</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CF_M05_P01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Microservices</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>The system is divided into small, independent, and autonomous services where each microservice is responsible for a specific functionality and communicates with others via messaging systems.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>9, 56</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Microservices</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Application has an architecture based on microservices.</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>CF_M05_P01</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CF_M05_AU14</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>ViewModel</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Frontend component responsible for logic, data processing, and service orchestration (TS).</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ViewModel</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>The ViewModel component groups the TS files of the components and the services they
 have associated with them. Each TS file defines the behavior of the application component
 to which it corresponds, taking care of data processing and validations</t>
         </is>
       </c>
-      <c r="P16" t="n">
+      <c r="P24" t="n">
         <v>64</v>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>CF_M05_AD03</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CF_M05_P03</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
         <is>
           <t>CF_M05_AU14</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="T24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CF_M05_AU33</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Spring Boot</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Backend framework used for developing microservices and REST APIs.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>61, 76</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Spring Boot</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Spring Boot is used, which provides a platform for exposing a REST API</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>61, 62</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CF_M05_AU37</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>CF_M05_AU33</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>CF_M05_AU13</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HTML and SCSS files responsible for screen presentation and capturing user input.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Frontend component responsible for UI presentation (HTML/SCSS).</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>['AU_10']</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
 each component that makes up the application. They are responsible for presenting the
 screens and capturing user interactions such as clicks or text entries.</t>
         </is>
       </c>
-      <c r="P17" t="n">
+      <c r="P26" t="n">
         <v>62</v>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>CF_M05_AD03</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>CF_M05_AU13</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CF_M05_AU23</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>The Portal Service communicates with the Leader Service for traffic routing and security.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>['AU_03', 'AU_02']</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>portal service, leader service</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">It can be observed that leader microservice communicates with Portal microservice. </t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>CF_M05_AU01, CF_M05_AU02</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>CF_M05_AU23</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>The Leader Service communicates with the Scheduler Service.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>56, 59</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>['AU_02', 'AU_06']</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>leader service, scheduler service</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Leader microservice communicates with Scheduler microservice. </t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>CF_M05_AU01, CF_M05_AU05</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>leader microservice, scheduler microservice</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CF_M05_AU24</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>The Leader Service communicates with the Access Control Service.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>56, 58</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>['AU_02', 'AU_04']</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>leader service, access control service</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">It can be observed that leader microservice communicates with Access Control microservice. </t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>CF_M05_AU01, CF_M05_AU03</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>CF_M05_AU24</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>leader microservice, access control microservice</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AU_33</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CF_M05_AU29</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>The ViewModel component communicates with the Model (Frontend) component.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>64, 66</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>['AU_12', 'AU_13']</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>AU_33</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>viewmodel, model (frontend)</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>CF_M05_AU14, CF_M05_AU15</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>CF_M05_AU29</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>viewmodel, model</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CF_M05_AD02</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>The application organizes code into two distinct components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>The application follows the Client-Server pattern which organizes the code into two distinct
-components: the client, which makes service requests, and the server, which receives,
-processes, and returns responses.</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Classification Changed</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>CF_M05_AD02</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CF_M05_AD01</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>The system is divided into small, independent, and autonomous services where each microservice is responsible for a specific functionality and communicates with others via messaging systems.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>9, 56</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Application has an architecture based on microservices.</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>CF_M05_AD01</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CF_M05_AU33</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Spring Boot</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Backend framework used for the server-side application.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>61, 76</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>['AU_14']</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Spring Boot</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Spring Boot is used, which provides a platform for exposing a REST API</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>61, 62</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>CF_M05_AU37</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>CF_M05_AU33</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CF_M05_AU10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Amazon RDS</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Managed database service for data persistence.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>['AU_07']</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Amazon RDS</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
-microservice and client. </t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>CF_M05_AD05</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>CF_M05_AU10</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CF_M05_AU07</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Amazon EKS</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Managed Kubernetes service for container orchestration.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>['AU_07']</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Amazon EKS</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
-which allows the use of Kubernetes (K8s), a container orchestration platform created by
-Google, without the need to install or maintain it. </t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>81</v>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_P03</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>CF_M05_AU07</t>
+          <t>CF_M05_AU13</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CF_M05_P05</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Cloud Architecture</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>The application is designed, deployed, and executed using cloud computing services (AWS) instead of local or physical servers, allowing for scalability, availability, and accessibility.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Cloud Architecture</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The application applies a cloud architecture . That is, the application is designed,
+deployed and executed using cloud services (cloud computing) instead of local or physical servers.</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>CF_M05_P05</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3186,7 +3223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3264,157 +3301,153 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.033</v>
+        <v>0.0343</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Amazon Web Services (AWS)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>user, portal service</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cloud provider hosting the system infrastructure.</t>
+          <t>The User communicates with the Portal Service via the internet.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M05_AU10</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Amazon RDS</t>
-        </is>
-      </c>
+          <t>CF_M05_AU27</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.3794</v>
+        <v>0.4143</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Server Layer (Backend)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>leader service, communication log service</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Handles business logic, security, and data persistence.</t>
+          <t>The Leader Service routes communications to the Communication Log Service.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M05_AU37</t>
+          <t>CF_M05_AU04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Communication Log Microservice</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.3573</v>
+        <v>0.6661</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Controller</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>scheduler service, amazon rds</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Handles REST API requests and responses.</t>
+          <t>The Scheduler Service reads from and writes to Amazon RDS.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M05_AU17</t>
+          <t>CF_M05_AU10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Presentation Layer (Controllers)</t>
+          <t>Amazon RDS</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4133</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DTO / Mapper</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>access control service, amazon rds</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Handles data transfer objects and conversion between models and external representations.</t>
+          <t>The Access Control Service reads from and writes to Amazon RDS.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M05_AU20</t>
+          <t>CF_M05_AU03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Contract Layer (DTO/Mappers)</t>
+          <t>Access Control Microservice</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.2503</v>
+        <v>0.4672</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3425,28 +3458,32 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>user, portal service</t>
+          <t>communication log service, amazon rds</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The User communicates with the Portal Service via the internet.</t>
+          <t>The Communication Log Service reads from and writes to Amazon RDS.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M05_AU27</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>CF_M05_AU04</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Communication Log Microservice</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>0.3682</v>
+        <v>0.4829</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3457,28 +3494,32 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>leader service, communication log service</t>
+          <t>portal service, amazon rds</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The Leader Service communicates with the Communication Log Service.</t>
+          <t>The Portal Service reads from and writes to Amazon RDS.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M05_AU25</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>CF_M05_AU10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>0.6552</v>
+        <v>0.4825</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3489,28 +3530,32 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>leader service, portal service</t>
+          <t>viewmodel, presentation layer (controller)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The Leader Service communicates with the Portal Service.</t>
+          <t>The ViewModel orchestrates HTTP calls to the backend Presentation Layer.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M05_AU23</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>CF_M05_AU14</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ViewModel</t>
+        </is>
+      </c>
       <c r="H9" t="n">
-        <v>0.5642</v>
+        <v>0.3219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3521,32 +3566,32 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>scheduler service, amazon rds</t>
+          <t>presentation layer (controller), business logic layer (service)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Scheduler Service communicates with Amazon RDS for data persistence.</t>
+          <t>The Presentation Layer communicates with the Business Logic Layer.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M05_AU10</t>
+          <t>CF_M05_AU18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Amazon RDS</t>
+          <t>Business Logic Layer (Services)</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.4667</v>
+        <v>0.5426</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3557,32 +3602,32 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>access control service, amazon rds</t>
+          <t>business logic layer (service), data access layer (repository)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Access Control Service communicates with Amazon RDS for data persistence.</t>
+          <t>The Business Logic Layer interacts with the Data Access Layer.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Access Control Microservice</t>
+          <t>Business Logic Layer (Services)</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.4402</v>
+        <v>0.5238</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3593,306 +3638,62 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>communication log service, amazon rds</t>
+          <t>data access layer (repository), amazon rds</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The Communication Log Service communicates with Amazon RDS for data persistence.</t>
+          <t>The Data Access Layer interacts with Amazon RDS.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_AU21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Communication Log Microservice</t>
+          <t>Data access layer (Repositories)</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.5246</v>
+        <v>0.4864</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>P_06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>portal service, amazon rds</t>
-        </is>
-      </c>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Single-Page Application (SPA)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>The Portal Service communicates with Amazon RDS for data persistence.</t>
+          <t>The client is developed as a Single-Page Application that renders dynamic views and manages internal navigation without reloading the page.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CF_M05_AU10</t>
+          <t>CF_M05_AU04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Amazon RDS</t>
+          <t>Communication Log Microservice</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.4757</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AU_32</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>presentation layer (frontend), viewmodel</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>The Presentation Layer communicates with the ViewModel component.</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Presentation Layer (Controllers)</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0.4574</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AU_34</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>viewmodel, controller</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>The ViewModel component sends HTTP requests to the Controller component.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>CF_M05_AU30</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
-        <v>0.3278</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AU_35</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>controller, service (backend)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>The Controller component communicates with the Service (Backend) component.</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>CF_M05_AU37</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>0.2506</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AU_36</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>service (backend), repository</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>The Service (Backend) component communicates with the Repository component.</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>CF_M05_AU37</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>0.2506</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AU_37</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>repository, model (backend)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>The Repository component communicates with the Model (Backend) component.</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>CF_M05_AU15</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>0.2469</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AU_38</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>service (backend), dto / mapper</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>The Service (Backend) component communicates with the DTO / Mapper component.</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>CF_M05_AU25</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="n">
-        <v>0.2349</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>P_06</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Single-Page Application (SPA)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>The client is developed as a Single-Page Application that renders dynamic views and manages internal navigation without reloading the page.</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>CF_M05_AU04</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Communication Log Microservice</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>0.1559</v>
+        <v>0.135</v>
       </c>
     </row>
   </sheetData>
@@ -3906,7 +3707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3954,21 +3755,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_AU08</t>
+          <t>CF_M05_AU06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SonarQube</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
+        <is>
+          <t>The client, also called the frontEnd, is responsible for the presentation and user experience
+of the application by encapsulating the interface logic and coordinating the calls to the server
+API.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>0.0819</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CF_M05_AU08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SonarQube</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
         <is>
           <t>SonarQube is a
 web application that statically analyses the code and offers recommendations and statistics
@@ -3976,274 +3811,240 @@
 problems, the amount of code covered in the tests, code duplication and code smells.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H3" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CF_M05_AU09</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Grafana</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>0.0195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AU11</t>
+          <t>CF_M05_AU09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Grafana</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
+          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CF_M05_AU11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ordering</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>These two microservices are responsible for
 calls to external services related to car sales.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Spring Boot</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>0.2069</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>0.2125</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>CF_M05_AU12</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>GSB</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
         <is>
           <t>These two microservices are responsible for
 calls to external services related to car sales.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>CF_M05_AU16</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Database</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AU_31</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>0.0968</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU18</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Business Logic Layer (Services)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Services provide the interface and implementation of all the application's business logic.</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Server Layer (Backend)</t>
+          <t>Data Access Layer (Repository)</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.1622</v>
+        <v>0.1214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M05_AU19</t>
+          <t>CF_M05_AU25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Domain Layer (Models)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>leader microservice, access control microservice</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Models represent the internal and persistent structure of the system entities, reflecting the
-stored information identically.</t>
+          <t xml:space="preserve">It can be observed that leader microservice communicates with Communication Log microservice. </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MVVM (Model-View-ViewModel)</t>
-        </is>
-      </c>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.1898</v>
+        <v>0.5965</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M05_AU20</t>
+          <t>CF_M05_AU27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Contract Layer (DTO/Mappers)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>portal microservice, presentation layer (controllers)</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
-request to be structured, providing a customized format based on response requirements.</t>
+          <t>Portal microservice communicates with the frontend indirectly through the Leader microservice</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DTO / Mapper</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.2503</v>
+        <v>0.4517</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M05_AU25</t>
+          <t>CF_M05_AU29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4254,28 +4055,32 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>leader microservice, access control microservice</t>
+          <t>viewmodel, model</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">It can be observed that leader microservice communicates with Communication Log microservice. </t>
+          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU_26</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ViewModel</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>0.6552</v>
+        <v>0.5221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M05_AU27</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4284,226 +4089,195 @@
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>portal microservice, presentation layer (controllers)</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>Portal microservice communicates with the frontend indirectly through the Leader microservice</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
-        <v>0.5286</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU28</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>viewmodel, view</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>AU_12</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ViewModel</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4976</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CF_M05_AU30</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
         <is>
           <t>The controllers, through specific
 functions, process the requests received, manage the validation of the information and channel
 the requests to the corresponding modules or services</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0.2629</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU31</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> the Repositories are responsible for performing queries on the database.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Data Access Layer (Repository)</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2089</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
+structure and normalize communication with the data layer. </t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AU_34</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.3278</v>
+        <v>0.0424</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
+          <t>CF_M05_AU35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> the Repositories are responsible for performing queries on the database.</t>
+          <t>The message
+exchange protocol used in this case is HTTP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Repository</t>
-        </is>
-      </c>
+          <t>AU_29</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.2747</v>
+        <v>0.2782</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
+          <t>CF_M05_AU37</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>Server (Backend)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
-structure and normalize communication with the data layer. </t>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
+responsibilities are separated:</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.0446</v>
+        <v>0.2932</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CF_M05_AU35</t>
+          <t>CF_M05_P06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Shared Database</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>The message
-exchange protocol used in this case is HTTP</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>AU_34</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
-        <v>0.2704</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CF_M05_AD06</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Shared Database</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>AU_31</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="n">
-        <v>0.0687</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Data Access Layer (Repository)</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.0864</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6304</v>
+        <v>0.7143</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6304</v>
+        <v>0.6522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8462</v>
+        <v>0.8571</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6667</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9217</v>
+        <v>0.9164</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.875</v>
+        <v>0.8889</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.75</v>
+        <v>0.5926</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8536</v>
+        <v>0.7985</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.75</v>
+        <v>0.7407</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6818</v>
+        <v>0.5833</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -559,10 +559,8 @@
           <t>fixes</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" t="n">
+        <v>0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -626,16 +624,16 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8095</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6296</v>
+        <v>0.7037</v>
       </c>
     </row>
     <row r="3">
@@ -670,16 +668,16 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.35</v>
+        <v>0.4286</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5385</v>
+        <v>0.4615</v>
       </c>
     </row>
   </sheetData>
@@ -725,7 +723,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -735,7 +733,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +743,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13 / 20</t>
+          <t>13 / 14</t>
         </is>
       </c>
     </row>
@@ -768,7 +766,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7 / 7</t>
+          <t>6 / 6</t>
         </is>
       </c>
     </row>
@@ -779,7 +777,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -789,7 +787,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +797,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6304</v>
+        <v>0.7143</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +807,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6304</v>
+        <v>0.6522</v>
       </c>
     </row>
     <row r="12">
@@ -888,22 +886,22 @@
         <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -916,22 +914,22 @@
         <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F3" t="n">
+        <v>27</v>
+      </c>
+      <c r="G3" t="n">
         <v>24</v>
       </c>
-      <c r="E3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F3" t="n">
-        <v>24</v>
-      </c>
-      <c r="G3" t="n">
-        <v>21</v>
-      </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -944,22 +942,22 @@
         <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -972,22 +970,22 @@
         <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -1000,22 +998,22 @@
         <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -1028,13 +1026,13 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1043,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1057,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1165,12 +1163,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M05_AU33</t>
+          <t>CF_M05_AU16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1179,67 +1177,69 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7665</v>
+        <v>0.7533</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kubernetes</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pel desplegament de l’aplicació s’ha fet ús d’Amazon EKS, un servei que ofereix AWS el qual permet utilitzar Kubernetes (K8s).</t>
+          <t>Repositories are responsible for performing queries on the database.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['P_02']</t>
+          <t>['AU_05', 'P_05']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
+          <t>the microservices are connected to a shared database that is decoupled per
+microservice and client. There is a schema for each microservice and each client has its
+own set of schemas per microservice.</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
+          <t>CF_M05_P06</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M05_AU33</t>
+          <t>CF_M05_AU16</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M05_AU02</t>
+          <t>CF_M05_AU33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1261,51 +1261,133 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.785</v>
+        <v>0.7665</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>El microservei del portal té com a funció principal oferir una interfície centralitzada per a l’accés a les diferents aplicacions de VWGS.</t>
+          <t>Container orchestration platform used for deployment.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['AU_22', 'P_02']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
+          <t>Docker</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>CF_M05_AU33</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CF_M05_AU02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>The portal microservice offers a centralized interface for accessing different VWGS applications.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>['P_01']</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>Portal Microservice</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">The portal microservice's main function is to provide a centralized interface for accessing the different VWGS
 applications. This component acts as an entry point for users, providing a unified experience. In addition to its
@@ -1313,184 +1395,102 @@
 itself and the rest of the portal's applications. </t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="P4" t="n">
         <v>57</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="T4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>CF_M05_AU01</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>0.7874</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Leader</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Aquest microservei té com a funció principal l’encaminament de totes les comunicacions cap al microservei corresponent dins de l’arquitectura del sistema.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>This microservice acts as a central point for traffic management and routing communications.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Leader Microservice</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>This microservice has as its main function the routing of all communications to the corresponding microservice
 within the system architecture. It acts as a central point for traffic management, ensuring that any interaction,
 both with external services and between internal microservices, is carried out in an orderly and secure manner.</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="P5" t="n">
         <v>57</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>CF_M05_AU01</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CF_M05_AU18</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.7929</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Capa de lògica de negoci</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>La capa de lògica de negoci aplica les regles del domini.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>['P_05']</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Business Logic Layer (Services)</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Services provide the interface and implementation of all the application's business logic.</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>CF_M05_P04</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M05_AU18</t>
+          <t>CF_M05_AU01</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1498,7 +1498,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>El proveïdor per aquest projecte és Amazon Web Services el qual té un ampli catàleg de serveis i recursos cloud.</t>
+          <t>Cloud provider for the system.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>60, 81</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1542,7 +1542,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1581,12 +1581,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M05_AU21</t>
+          <t>CF_M05_AU05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1595,133 +1595,51 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8361</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Capa d’accés a dades</t>
+          <t>Scheduler</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>La capa d’accés a dades interactua amb la base de dades.</t>
+          <t>This microservice is responsible for the planning and programming of processes within the system.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['P_05']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Data access layer (Repositories)</t>
+          <t>Scheduler Microservice</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
-        <is>
-          <t>the Repositories are responsible for performing queries on the database.</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>CF_M05_P04</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU21</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CF_M05_AU05</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.8361</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Scheduler</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Té com a funció principal la planificació i programació de processos dins del sistema.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>['P_01']</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Scheduler Microservice</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
         <is>
           <t>Its main function is the
 planning and scheduling of processes within the system. This component allows you to define,
@@ -1731,84 +1649,84 @@
 microservices.</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="P7" t="n">
         <v>59.6</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
         <is>
           <t>CF_M05_AU05</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="T7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D8" t="n">
         <v>0.8378</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Communication Log</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>El microservei Communication Log té com a finalitat principal registrar totes les comunicacions que es produeixen dins del sistema, tant entre microserveis com amb serveis externs.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>This microservice registers all communications within the system for traceability and auditing.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Communication Log Microservice</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>The main purpose of the Communication Log microservice is to record all
 communications that occur within the system, both between microservices and with external
@@ -1818,8 +1736,91 @@
 and faster analysis.</t>
         </is>
       </c>
+      <c r="P8" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CF_M05_P01</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU04</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8439</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>This microservice manages user authentication and permissions.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>['P_01']</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Access Control Microservice</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The main objective of the Access Control microservice is to manage user authentication and
+permissions within the application. </t>
+        </is>
+      </c>
       <c r="P9" t="n">
-        <v>58.59</v>
+        <v>58</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1829,7 +1830,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_AU03</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1837,12 +1838,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1851,68 +1852,68 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8439</v>
+        <v>0.8441</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>Contract Layer</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>El microservei Access Control té com a objectiu principal la gestió d’autenticació d’usuaris i els seus permisos dins de l’aplicació.</t>
+          <t>A transversal layer that separates the internal model from the external API representation.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>68, 73</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['P_05']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Access Control Microservice</t>
+          <t>Contract Layer (DTO/Mappers)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">The main objective of the Access Control microservice is to manage user authentication and
-permissions within the application. </t>
+          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
+request to be structured, providing a customized format based on response requirements.</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CF_M05_P01</t>
+          <t>CF_M05_P04</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU20</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1920,65 +1921,400 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M05_P04</t>
+          <t>CF_M05_AU17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.9122</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Layered Architecture</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated: the presentation layer receives requests and builds responses, the business logic layer applies domain rules, the data access layer interacts with the database, and the domain layer defines the data model.</t>
+          <t>The presentation layer is responsible for displaying information to the user and capturing interactions.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>61, 68</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['P_05']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
+          <t>Presentation Layer (Controllers)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>The controllers, through specific
+functions, process the requests received, manage the validation of the information and channel
+the requests to the corresponding modules or services of the data layer.</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AU_05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU21</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9164</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Access Layer</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>This layer interacts with the database.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>68, 74</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>['P_05']</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>AU_05</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Data access layer (Repositories)</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>the Repositories are responsible for performing queries on the database.</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU21</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AU_06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU19</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9445</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Domain Layer</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>The domain layer defines the data model.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>68, 71</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>['P_05']</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>AU_06</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Domain Layer (Models)</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Models represent the internal and persistent structure of the system entities, reflecting the
+stored information identically.</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU19</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CF_M05_AU18</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.9562</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Business Logic Layer</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>This layer applies the domain rules and processes the information.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>68, 70</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>['P_05']</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Business Logic Layer (Services)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Services provide the interface and implementation of all the application's business logic.</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>CF_M05_AU18</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P_05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Layered Architecture</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spring Boot organitza el codi seguint el patró a capes amb les quals se separen responsabilitats: la capa de presentació rep les peticions i construeix les respostes, la capa de lògica de negoci aplica les regles del domini, la capa d’accés a dades interactua amb la base de dades i la capa de domini defineix el model de dades.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>['P_03', 'AU_19']</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>The document refers to this as 'patró a capes' (Layered Pattern/Architecture) within the server component.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>P_05</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Layered Architecture</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Layered architecture is used: Spring Boot organizes the code following the pattern of layers with which
 responsibilities are separated: the presentation layer receives requests and constructs responses, the
@@ -1986,512 +2322,188 @@
 separates the internal model from the external representation of the API.</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>68-69</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
         <is>
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="T15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>CF_M05_P05</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>pattern</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Cloud Architecture</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>The application is designed, deployed, and executed using cloud services (cloud computing) instead of local or physical servers.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>L’aplicació està dissenyada, desplegada i executada utilitzant serveis al núvol (cloud computing) en lloc de servidors locals o físics propis.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>Cloud Architecture</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t xml:space="preserve"> The application applies a cloud architecture . That is, the application is designed,
 deployed and executed using cloud services (cloud computing) instead of local or physical servers.</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="P16" t="n">
         <v>60</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
         <is>
           <t>CF_M05_P05</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CF_M05_AU12</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="T16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CF_M05_AU13</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>GSB</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Aquests dos microserveis s’encarreguen de les crides cap a serveis externs relacionades amb la venda d’automòbils.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>['P_01']</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>GSB</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>These two microservices are responsible for
-calls to external services related to car sales.</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>CF_M05_P01</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>CF_M05_AU12</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CF_M05_AU31</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>El protocol d’intercanvi de missatges que es fa servir en aquest cas és HTTP.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>['P_03']</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>The message
-exchange protocol used in this case is HTTP</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>CF_M05_AU31</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AU_12</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CF_M05_AU13</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>El component que anomenem View, Vista en català, està format pels fitxers HTML i SCSS de cada component que conformen l’aplicació.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>The View component is responsible for the presentation of screens and capturing user interactions.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>['P_04']</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>AU_12</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>['AU_03', 'P_04']</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
 each component that makes up the application. They are responsible for presenting the
 screens and capturing user interactions such as clicks or text entries.</t>
         </is>
       </c>
-      <c r="P15" t="n">
+      <c r="P17" t="n">
         <v>62</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>CF_M05_AU13</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CF_M05_AU27</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>El component que anomenem View, Vista en català, està format pels fitxers HTML i SCSS de cada component que conformen l’aplicació. [...] El component ViewModel agrupa els fitxers TS dels components i els serveis que tenen associats. [...] Els Models són les classes TypeScript que defineixen el contracte de dades consumit per la vista i pel ViewModel.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>62,64,66</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>['AU_12', 'AU_13', 'AU_14']</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>view, viewmodel, model</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CF_M05_AU14, CF_M05_AU13, CF_M05_AU15 </t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>CF_M05_AU27</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>viewmodel, view, model</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>El microservei Communication Log té com a finalitat principal registrar totes les comunicacions que es produeixen dins del sistema, tant entre microserveis com amb serveis externs.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>['AU_04', 'AU_01', 'AU_02', 'AU_03', 'AU_05', 'AU_06', 'AU_07']</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>communication log, leader, portal, access control, scheduler, ordering, gsb</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
-        </is>
-      </c>
+          <t>CF_M05_AU13</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M05_AU11</t>
+          <t>CF_M05_AU31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2504,64 +2516,60 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Aquests dos microserveis s’encarreguen de les crides cap a serveis externs relacionades amb la venda d’automòbils.</t>
+          <t>Communication protocol used for message exchange.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['AU_08']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>These two microservices are responsible for
-calls to external services related to car sales.</t>
+          <t>The message
+exchange protocol used in this case is HTTP</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>CF_M05_P01</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M05_AU11</t>
+          <t>CF_M05_AU31</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2569,573 +2577,813 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M05_AU29</t>
+          <t>CF_M05_AU27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Spring Boot</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pel servidor s’ha utilitzat Spring Boot, que proporciona una plataforma per exposar una API REST.</t>
+          <t>The View component is responsible for capturing user interactions, while the ViewModel acts as an intermediary between the View and the Model, managing data processing and user actions.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62,64</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['P_03']</t>
+          <t>['AU_13', 'AU_14', 'AU_15']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Spring Boot</t>
-        </is>
-      </c>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>view, viewmodel, model</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Spring Boot is used, which provides a platform for exposing a REST API</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>61, 62</t>
-        </is>
-      </c>
+          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
+          <t xml:space="preserve">CF_M05_AU14, CF_M05_AU13, CF_M05_AU15 </t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M05_AU29</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>CF_M05_AU27</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>viewmodel, view, model</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M05_P03</t>
+          <t>CF_M05_AU25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>MVVM</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
+          <t>The services call the corresponding functions to obtain the result of the request.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['P_01']</t>
+          <t>['AU_04', 'AU_17']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>business logic layer, repository</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Data access and logic management in this project is carried out using REST operations, which structure and normalize communication with the data layer.</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17, CF_M05_AU21</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>CF_M05_AU25</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>presentation layer (controllers), data access layer (repositories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CF_M05_AU26</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Repositories are responsible for performing queries on the database.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>['AU_17', 'AU_05']</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>repository, data access layer</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>This technology helps us in the communication between the data layer and the database of the project application.</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CF_M05_AU21, CF_M05_AU16</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>CF_M05_AU26</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>data access layer (repositories), database</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Spring Boot</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Framework used for the backend development.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>61, 76</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>['AU_04', 'P_05']</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Spring Boot</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Spring Boot is used, which provides a platform for exposing a REST API</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>61, 62</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CF_M05_P03</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>MVVM</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Angular aplica el patró MVVM (Model-View-ViewModel), ja que la seva arquitectura està basada en components i serveis.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>['P_03', 'AU_18']</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>MVVM</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t xml:space="preserve">Angular applies the MVVM pattern (Model-View-ViewModel), since its architecture is
 based on components and services. </t>
         </is>
       </c>
-      <c r="P20" t="n">
+      <c r="P23" t="n">
         <v>62</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr">
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="T23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>CF_M05_AU30</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Angular</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>El client s’ha desenvolupat amb Angular, implementant una Single-Page Application (SPA).</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>['P_03']</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Framework used for the frontend development.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>61, 76</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>['AU_03', 'P_04']</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
         <is>
           <t>Angular</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>In the present project, the client has been developed with Angular</t>
         </is>
       </c>
-      <c r="P21" t="n">
+      <c r="P24" t="n">
         <v>61</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
         <is>
           <t>CF_M05_AU30</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="T24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>pattern</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D25" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Microservices</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>The application has an architecture based on microservices, which consists of dividing the system into a set of small, independent, and autonomous services where each microservice is responsible for a specific functionality.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Consisteix a dividir el sistema en un conjunt de serveis petits, independents i autònoms on cada microservei s’encarrega d’una funcionalitat específica i es comunica amb la resta mitjançant diversos sistemes de missatgeria.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
         <is>
           <t>Microservices</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Application has an architecture based on microservices.</t>
         </is>
       </c>
-      <c r="P22" t="n">
+      <c r="P25" t="n">
         <v>56</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr">
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="T25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>CF_M05_AU15</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Els Models són les classes TypeScript que defineixen el contracte de dades consumit per la vista i pel ViewModel.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>The Model defines the data contract consumed by the view and ViewModel.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>['P_04']</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>['AU_03', 'P_04']</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Models are the TypeScript classes that define the data contract consumed by the
 view and the ViewModel. These classes allow the View to know what data to display and
 the ViewModel to know how to manipulate it</t>
         </is>
       </c>
-      <c r="P23" t="n">
+      <c r="P26" t="n">
         <v>66</v>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr">
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
         <is>
           <t>CF_M05_AU15</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="T26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>pattern</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D27" t="n">
         <v>1</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Design Pattern</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>L’aplicació segueix el patró Client-Servidor el qual organitza el codi en dos components diferenciats: el client, que formula sol·licituds de servei, i el servidor, que les rep, les processa i retorna respostes.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>['P_01']</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
         <is>
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>The application follows the Client-Server pattern which organizes the code into two distinct
 components: the client, which makes service requests, and the server, which receives,
 processes, and returns responses.</t>
         </is>
       </c>
-      <c r="P24" t="n">
+      <c r="P27" t="n">
         <v>61</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
         <is>
           <t>Classification Changed</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="T27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>CF_M05_AU14</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D28" t="n">
         <v>1</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>ViewModel</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>El component ViewModel agrupa els fitxers TS dels components i els serveis que tenen associats.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>The ViewModel acts as an intermediary between the View and the Model, managing data processing and user actions.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>['P_04']</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>['AU_03', 'P_04']</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
         <is>
           <t>ViewModel</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>The ViewModel component groups the TS files of the components and the services they
 have associated with them. Each TS file defines the behavior of the application component
 to which it corresponds, taking care of data processing and validations</t>
         </is>
       </c>
-      <c r="P25" t="n">
+      <c r="P28" t="n">
         <v>64</v>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
         <is>
           <t>CF_M05_AU14</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3148,7 +3396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3196,151 +3444,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>User</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El format de dades emprat és JSON.</t>
+          <t>The user is the actor that accesses the portal and applications.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
+          <t>CF_M05_AU13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>View</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.678</v>
+        <v>0.7551</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Capa de presentació</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>La capa de presentació rep les peticions i construeix les respostes.</t>
+          <t>The administrator is a user with additional permissions to manage application access.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M05_AU17</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Presentation Layer (Controllers)</t>
+          <t>Server (Backend)</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.701</v>
+        <v>0.6979</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Capa de domini</t>
+          <t>Controller</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>La capa de domini defineix el model de dades.</t>
+          <t>Controllers process received requests, manage validation, and channel requests to the data layer.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M05_AU19</t>
+          <t>CF_M05_AU17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Domain Layer (Models)</t>
+          <t>Presentation Layer (Controllers)</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.6918</v>
+        <v>0.7563</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Capa de contracte</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S’hi afegeix una capa transversal de contracte que separa el model intern de la representació externa de l’API.</t>
+          <t>Data format used for message exchange.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M05_AU20</t>
+          <t>CF_M05_AU31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Contract Layer (DTO/Mappers)</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.6848</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3351,32 +3599,32 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>angular, spring boot, http, json</t>
+          <t>user, portal</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El client s’ha desenvolupat amb Angular, implementant una Single-Page Application (SPA). [...] El protocol d’intercanvi de missatges que es fa servir en aquest cas és HTTP. [...] El format de dades emprat és JSON.</t>
+          <t>The user accesses the portal and applications.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
+          <t>CF_M05_AU02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Portal Microservice</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.7501</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3387,32 +3635,28 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>capa de presentació, capa de lògica de negoci, capa d’accés a dades, capa de domini, capa de contracte</t>
+          <t>leader, portal, access control, communication log, scheduler</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>La capa de presentació rep les peticions i construeix les respostes, la capa de lògica de negoci aplica les regles del domini, la capa d’accés a dades interactua amb la base de dades i la capa de domini defineix el model de dades. S’hi afegeix una capa transversal de contracte que separa el model intern de la representació externa de l’API.</t>
+          <t>The Leader microservice routes all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M05_AU19</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Domain Layer (Models)</t>
-        </is>
-      </c>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.7736</v>
+        <v>0.9520999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3423,28 +3667,32 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>portal, leader</t>
+          <t>portal, view, viewmodel, model</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>En cada portal es realitzen els controls d’autentificació i autorització pertinents amb ajuda del Leader el qual decideix a quin domini funcional s’ha d’encaminar cada usuari.</t>
+          <t>The portal microservice incorporates the binaries necessary for the frontEnd of both the portal itself and the rest of the portal applications.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>CF_M05_AU02</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Portal Microservice</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>0.75</v>
+        <v>0.8185</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3455,22 +3703,62 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>leader, access control, communication log, scheduler, ordering, gsb</t>
+          <t>viewmodel, controller</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aquest microservei té com a funció principal l’encaminament de totes les comunicacions cap al microservei corresponent dins de l’arquitectura del sistema. [...] Actua com a punt central de gestió del trànsit, garantint que qualsevol interacció, tant amb serveis externs com entre microserveis interns, es realitzi de manera ordenada i segura.</t>
+          <t>The services are responsible for orchestrating HTTP calls to the server.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>CF_M05_AU31</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="H9" t="n">
-        <v>0.8071</v>
+        <v>0.7796999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AU_29</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>controller, business logic layer</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Controllers process received requests, manage validation, and channel requests to the data layer.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Presentation Layer (Controllers)</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7791</v>
       </c>
     </row>
   </sheetData>
@@ -3484,7 +3772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3593,7 +3881,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3632,7 +3920,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3668,7 +3956,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3683,387 +3971,291 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AU16</t>
+          <t>CF_M05_AU11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>These two microservices are responsible for
+calls to external services related to car sales.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6729000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CF_M05_AU12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GSB</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>These two microservices are responsible for
+calls to external services related to car sales.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6268</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0.9520999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Communication Log</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7702</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU24</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>client(frontend), server (backend)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7956</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU28</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
+structure and normalize communication with the data layer. </t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6758999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Server (Backend)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
+responsibilities are separated:</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7968</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M05_P06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Shared Database</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Capa d’accés a dades</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.7621</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Presentation Layer (Controllers)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>The controllers, through specific
-functions, process the requests received, manage the validation of the information and channel
-the requests to the corresponding modules or services of the data layer.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
-        <v>0.7357</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CF_M05_AU19</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Domain Layer (Models)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Models represent the internal and persistent structure of the system entities, reflecting the
-stored information identically.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
-        <v>0.7736</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CF_M05_AU20</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Contract Layer (DTO/Mappers)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
-request to be structured, providing a customized format based on response requirements.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>0.7462</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU23</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M05_AU24</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>client(frontend), server (backend)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.7956</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU25</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>presentation layer (controllers), data access layer (repositories)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data access and logic management in this project is carried out using REST operations, which structure and normalize communication with the data layer.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
-        <v>0.7268</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CF_M05_AU26</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>data access layer (repositories), database</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>This technology helps us in the communication between the data layer and the database of the project application.</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Capa d’accés a dades</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.7163</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CF_M05_AU28</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
-structure and normalize communication with the data layer. </t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0.6758999999999999</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CF_M05_AU32</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Server (Backend)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
-responsibilities are separated:</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>0.7968</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CF_M05_P06</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Shared Database</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>the microservices are connected to a shared database that is decoupled per
-microservice and client. There is a schema for each microservice and each client has its
-own set of schemas per microservice.</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Capa d’accés a dades</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>0.6917</v>
+        <v>0.6965</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7143</v>
+        <v>0.7027</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6522</v>
+        <v>0.5652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8571</v>
+        <v>0.9167</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.6667</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9164</v>
+        <v>0.9085</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8889</v>
+        <v>0.8333</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5926</v>
+        <v>0.75</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7985</v>
+        <v>0.8335</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7407</v>
+        <v>0.2083</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5833</v>
+        <v>0.7059</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -559,8 +559,10 @@
           <t>fixes</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -624,16 +626,16 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7037</v>
+        <v>0.6296</v>
       </c>
     </row>
     <row r="3">
@@ -668,16 +670,16 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4286</v>
+        <v>0.3077</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4615</v>
+        <v>0.3077</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -733,7 +735,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -743,7 +745,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -754,7 +756,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13 / 14</t>
+          <t>13 / 13</t>
         </is>
       </c>
     </row>
@@ -766,7 +768,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6 / 6</t>
+          <t>4 / 4</t>
         </is>
       </c>
     </row>
@@ -777,7 +779,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -787,7 +789,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -797,7 +799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7143</v>
+        <v>0.7027</v>
       </c>
     </row>
     <row r="11">
@@ -807,7 +809,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6522</v>
+        <v>0.5652</v>
       </c>
     </row>
     <row r="12">
@@ -886,22 +888,22 @@
         <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="n">
         <v>24</v>
-      </c>
-      <c r="E2" t="n">
-        <v>24</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -914,22 +916,22 @@
         <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="n">
         <v>24</v>
-      </c>
-      <c r="H3" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -942,22 +944,22 @@
         <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -970,22 +972,22 @@
         <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -998,22 +1000,22 @@
         <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
         <v>24</v>
-      </c>
-      <c r="F6" t="n">
-        <v>21</v>
-      </c>
-      <c r="G6" t="n">
-        <v>14</v>
-      </c>
-      <c r="H6" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -1026,13 +1028,13 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1041,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1055,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T28"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1163,12 +1165,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M05_AU16</t>
+          <t>CF_M05_AU13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1177,43 +1179,39 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7533</v>
+        <v>0.7551</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>User</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Repositories are responsible for performing queries on the database.</t>
+          <t>The user is the actor who accesses the portal and applications.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>['AU_05', 'P_05']</t>
-        </is>
-      </c>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>View</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1223,23 +1221,23 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>the microservices are connected to a shared database that is decoupled per
-microservice and client. There is a schema for each microservice and each client has its
-own set of schemas per microservice.</t>
+          <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
+each component that makes up the application. They are responsible for presenting the
+screens and capturing user interactions such as clicks or text entries.</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CF_M05_P06</t>
+          <t>CF_M05_P03</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CF_M05_AU16</t>
+          <t>CF_M05_AU13</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -1247,12 +1245,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M05_AU33</t>
+          <t>CF_M05_AU07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1261,7 +1259,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7665</v>
+        <v>0.7569</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1275,29 +1273,29 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Container orchestration platform used for deployment.</t>
+          <t>Kubernetes is a container orchestration platform used for deployment.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['AU_22', 'P_02']</t>
+          <t>['AU_15']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Amazon EKS</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1307,7 +1305,9 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
+          <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
+which allows the use of Kubernetes (K8s), a container orchestration platform created by
+Google, without the need to install or maintain it. </t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1315,13 +1315,13 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
+          <t>CF_M05_P05</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M05_AU33</t>
+          <t>CF_M05_AU07</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>The portal microservice offers a centralized interface for accessing different VWGS applications.</t>
+          <t>The portal microservice has as its main function to offer a centralized interface for access to the different VWGS applications.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>This microservice acts as a central point for traffic management and routing communications.</t>
+          <t>This microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1526,23 +1526,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cloud provider for the system.</t>
+          <t>The provider for this project is Amazon Web Services which has a wide catalog of cloud services and resources.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>60, 81</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>['P_02']</t>
-        </is>
-      </c>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1609,12 +1605,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>This microservice is responsible for the planning and programming of processes within the system.</t>
+          <t>This microservice has as its main function the planning and programming of processes within the system.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1696,12 +1692,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>This microservice registers all communications within the system for traceability and auditing.</t>
+          <t>The Communication Log microservice has as its main purpose to record all communications that occur within the system.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1783,12 +1779,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>This microservice manages user authentication and permissions.</t>
+          <t>The Access Control microservice has as its main objective the management of user authentication and their permissions within the application.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1866,12 +1862,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A transversal layer that separates the internal model from the external API representation.</t>
+          <t>The contract layer separates the internal model from the external representation of the API.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>68, 73</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1949,12 +1945,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>The presentation layer is responsible for displaying information to the user and capturing interactions.</t>
+          <t>The presentation layer receives requests and builds responses.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>61, 68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2033,12 +2029,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>This layer interacts with the database.</t>
+          <t>The data access layer interacts with the database.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>68, 74</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2120,7 +2116,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>68, 71</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2198,12 +2194,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>This layer applies the domain rules and processes the information.</t>
+          <t>The business logic layer applies the domain rules.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>68, 70</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2280,7 +2276,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Spring Boot organitza el codi seguint el patró a capes amb les quals se separen responsabilitats: la capa de presentació rep les peticions i construeix les respostes, la capa de lògica de negoci aplica les regles del domini, la capa d’accés a dades interactua amb la base de dades i la capa de domini defineix el model de dades.</t>
+          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated: the presentation layer receives requests and builds responses, the business logic layer applies domain rules, the data access layer interacts with the database, and the domain layer defines the data model.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2290,14 +2286,10 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['P_03', 'AU_19']</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>The document refers to this as 'patró a capes' (Layered Pattern/Architecture) within the server component.</t>
-        </is>
-      </c>
+          <t>['P_03', 'AU_14']</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>P_05</t>
@@ -2322,10 +2314,8 @@
 separates the internal model from the external representation of the API.</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>68-69</t>
-        </is>
+      <c r="P15" t="n">
+        <v>68.69</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -2367,7 +2357,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>L’aplicació està dissenyada, desplegada i executada utilitzant serveis al núvol (cloud computing) en lloc de servidors locals o físics propis.</t>
+          <t>The application is designed, deployed, and executed using cloud services (cloud computing) instead of local or physical servers.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2414,12 +2404,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M05_AU13</t>
+          <t>CF_M05_AU33</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2432,65 +2422,59 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>The View component is responsible for the presentation of screens and capturing user interactions.</t>
+          <t>Docker is used to create images for each microservice.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>['AU_03', 'P_04']</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
-each component that makes up the application. They are responsible for presenting the
-screens and capturing user interactions such as clicks or text entries.</t>
+          <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M05_P03</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M05_AU13</t>
+          <t>CF_M05_AU33</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2498,7 +2482,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2526,23 +2510,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Communication protocol used for message exchange.</t>
+          <t>The exchange protocol used for communication between client and server.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>['AU_08']</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2577,12 +2557,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M05_AU27</t>
+          <t>CF_M05_AU25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2601,28 +2581,28 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The View component is responsible for capturing user interactions, while the ViewModel acts as an intermediary between the View and the Model, managing data processing and user actions.</t>
+          <t>The presentation layer (frontEnd) communicates with the server (backEnd) via HTTP.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>62,64</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_13', 'AU_14', 'AU_15']</t>
+          <t>['AU_03', 'AU_04']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>view, viewmodel, model</t>
+          <t>presentation layer, business logic layer</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2633,36 +2613,38 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>Data access and logic management in this project is carried out using REST operations, which structure and normalize communication with the data layer.</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>69</v>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CF_M05_AU14, CF_M05_AU13, CF_M05_AU15 </t>
+          <t>CF_M05_AU17, CF_M05_AU21</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M05_AU27</t>
+          <t>CF_M05_AU25</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>viewmodel, view, model</t>
+          <t>presentation layer (controllers), data access layer (repositories)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M05_AU25</t>
+          <t>CF_M05_AU26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2681,7 +2663,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>The services call the corresponding functions to obtain the result of the request.</t>
+          <t>The business logic layer (Services) calls the corresponding functions to obtain the result of the request.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2691,18 +2673,18 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_17']</t>
+          <t>['AU_04', 'AU_05']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>business logic layer, repository</t>
+          <t>business logic layer, data access layer</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2713,125 +2695,127 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Data access and logic management in this project is carried out using REST operations, which structure and normalize communication with the data layer.</t>
+          <t>This technology helps us in the communication between the data layer and the database of the project application.</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M05_AU17, CF_M05_AU21</t>
+          <t>CF_M05_AU21, CF_M05_AU16</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M05_AU25</t>
+          <t>CF_M05_AU26</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>presentation layer (controllers), data access layer (repositories)</t>
+          <t>data access layer (repositories), database</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M05_AU26</t>
+          <t>CF_M05_AU29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Spring Boot</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Repositories are responsible for performing queries on the database.</t>
+          <t>Spring Boot is a framework used to accelerate the development of microservices and enterprise applications.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['AU_17', 'AU_05']</t>
+          <t>['AU_08', 'AU_09', 'AU_10', 'AU_11', 'AU_12', 'P_05']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_31</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>repository, data access layer</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Spring Boot</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>This technology helps us in the communication between the data layer and the database of the project application.</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>76</v>
+          <t>Spring Boot is used, which provides a platform for exposing a REST API</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>61, 62</t>
+        </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CF_M05_AU21, CF_M05_AU16</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M05_AU26</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>data access layer (repositories), database</t>
-        </is>
-      </c>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M05_AU29</t>
+          <t>CF_M05_P03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2839,65 +2823,60 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spring Boot</t>
+          <t>MVVM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Framework used for the backend development.</t>
+          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>61, 76</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['AU_04', 'P_05']</t>
+          <t>['P_03', 'AU_13']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Spring Boot</t>
+          <t>MVVM</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Spring Boot is used, which provides a platform for exposing a REST API</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>61, 62</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>CF_M05_AU32</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Angular applies the MVVM pattern (Model-View-ViewModel), since its architecture is
+based on components and services. </t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CF_M05_AU29</t>
+          <t>CF_M05_P03</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2905,17 +2884,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M05_P03</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2923,60 +2902,63 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MVVM</t>
+          <t>Angular</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Angular aplica el patró MVVM (Model-View-ViewModel), ja que la seva arquitectura està basada en components i serveis.</t>
+          <t>Angular is a web development framework used for the frontEnd of the application.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['P_03', 'AU_18']</t>
+          <t>['AU_09', 'P_04']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>MVVM</t>
+          <t>Angular</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Angular applies the MVVM pattern (Model-View-ViewModel), since its architecture is
-based on components and services. </t>
+          <t>In the present project, the client has been developed with Angular</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CF_M05_AU06</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CF_M05_P03</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2984,17 +2966,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -3002,63 +2984,55 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Angular</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Framework used for the frontend development.</t>
+          <t>The application has an architecture based on microservices, which consists of dividing the system into a set of small, independent, and autonomous services where each microservice is responsible for a specific functionality.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>61, 76</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>['AU_03', 'P_04']</t>
-        </is>
-      </c>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Angular</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>In the present project, the client has been developed with Angular</t>
+          <t>Application has an architecture based on microservices.</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>CF_M05_AU06</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3066,12 +3040,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M05_P01</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3084,35 +3058,35 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Consisteix a dividir el sistema en un conjunt de serveis petits, independents i autònoms on cada microservei s’encarrega d’una funcionalitat específica i es comunica amb la resta mitjançant diversos sistemes de missatgeria.</t>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3121,269 +3095,27 @@
         </is>
       </c>
       <c r="O25" t="inlineStr">
-        <is>
-          <t>Application has an architecture based on microservices.</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>CF_M05_P01</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CF_M05_AU15</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>The Model defines the data contract consumed by the view and ViewModel.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>['AU_03', 'P_04']</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Models are the TypeScript classes that define the data contract consumed by the
-view and the ViewModel. These classes allow the View to know what data to display and
-the ViewModel to know how to manipulate it</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>CF_M05_P03</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>CF_M05_AU15</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>CF_M05_P02</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>L’aplicació segueix el patró Client-Servidor el qual organitza el codi en dos components diferenciats: el client, que formula sol·licituds de servei, i el servidor, que les rep, les processa i retorna respostes.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
         <is>
           <t>The application follows the Client-Server pattern which organizes the code into two distinct
 components: the client, which makes service requests, and the server, which receives,
 processes, and returns responses.</t>
         </is>
       </c>
-      <c r="P27" t="n">
+      <c r="P25" t="n">
         <v>61</v>
       </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
         <is>
           <t>Classification Changed</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CF_M05_AU14</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>ViewModel</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>The ViewModel acts as an intermediary between the View and the Model, managing data processing and user actions.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>['AU_03', 'P_04']</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>ViewModel</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>The ViewModel component groups the TS files of the components and the services they
-have associated with them. Each TS file defines the behavior of the application component
-to which it corresponds, taking care of data processing and validations</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>64</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>CF_M05_P03</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>CF_M05_AU14</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3396,7 +3128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3444,7 +3176,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3454,99 +3186,95 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The user is the actor that accesses the portal and applications.</t>
+          <t>The administrator is a user with additional permissions to manage application access for users.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M05_AU13</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Server (Backend)</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.7551</v>
+        <v>0.6979</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The administrator is a user with additional permissions to manage application access.</t>
+          <t>The data format used for communication.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
+          <t>CF_M05_AU31</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Server (Backend)</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.6979</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Controller</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>leader, portal, access control, communication log, scheduler</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Controllers process received requests, manage validation, and channel requests to the data layer.</t>
+          <t>The Leader microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Presentation Layer (Controllers)</t>
-        </is>
-      </c>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.7563</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="5">
@@ -3557,38 +3285,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>portal, leader, access control, communication log, scheduler</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data format used for message exchange.</t>
+          <t>The portal microservice has as its main function to offer a centralized interface for access to the different VWGS applications. [...] This component acts as an entry point for users, providing a unified experience.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
+          <t>CF_M05_AU02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Portal Microservice</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.678</v>
+        <v>0.8241000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3599,32 +3327,28 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>user, portal</t>
+          <t>communication log, leader, portal, access control, scheduler</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The user accesses the portal and applications.</t>
+          <t>The Communication Log microservice has as its main purpose to record all communications that occur within the system, both between microservices and with external services.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M05_AU02</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Portal Microservice</t>
-        </is>
-      </c>
+          <t>CF_M05_AU23</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.7501</v>
+        <v>0.9822</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3635,28 +3359,32 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>leader, portal, access control, communication log, scheduler</t>
+          <t>user, portal</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The Leader microservice routes all communications to the corresponding microservice within the system architecture.</t>
+          <t>The user accesses the portal and applications.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>CF_M05_AU02</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Portal Microservice</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.7501</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3667,32 +3395,32 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>portal, view, viewmodel, model</t>
+          <t>presentation layer, business logic layer</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The portal microservice incorporates the binaries necessary for the frontEnd of both the portal itself and the rest of the portal applications.</t>
+          <t>The presentation layer (Controllers) processes the requests received, manages the validation of the information and channels the requests to the corresponding modules or services of the data layer.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M05_AU02</t>
+          <t>CF_M05_AU17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Portal Microservice</t>
+          <t>Presentation Layer (Controllers)</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8185</v>
+        <v>0.8548</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3703,62 +3431,26 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>viewmodel, controller</t>
+          <t>data access layer, domain layer</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The services are responsible for orchestrating HTTP calls to the server.</t>
+          <t>The data access layer (Repositories) is responsible for performing queries on the database.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
+          <t>CF_M05_AU21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Data access layer (Repositories)</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.7796999999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>controller, business logic layer</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Controllers process received requests, manage validation, and channel requests to the data layer.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Presentation Layer (Controllers)</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.7791</v>
+        <v>0.9316</v>
       </c>
     </row>
   </sheetData>
@@ -3772,7 +3464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3858,7 +3550,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AU07</t>
+          <t>CF_M05_AU08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3868,49 +3560,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amazon EKS</t>
+          <t>SonarQube</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
-which allows the use of Kubernetes (K8s), a container orchestration platform created by
-Google, without the need to install or maintain it. </t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Amazon Web Services</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.7812</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CF_M05_AU08</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SonarQube</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
         <is>
           <t>SonarQube is a
 web application that statically analyses the code and offers recommendations and statistics
@@ -3918,9 +3572,45 @@
 problems, the amount of code covered in the tests, code duplication and code smells.</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Kubernetes</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6439</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CF_M05_AU09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Grafana</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3929,49 +3619,50 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.6439</v>
+        <v>0.6829</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AU09</t>
+          <t>CF_M05_AU11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Grafana</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
+          <t>These two microservices are responsible for
+calls to external services related to car sales.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kubernetes</t>
+          <t>User</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.6829</v>
+        <v>0.6729000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AU11</t>
+          <t>CF_M05_AU12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3981,7 +3672,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>GSB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -3993,269 +3684,378 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M05_AU12</t>
+          <t>CF_M05_AU14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GSB</t>
+          <t>ViewModel</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>These two microservices are responsible for
-calls to external services related to car sales.</t>
+          <t>The ViewModel component groups the TS files of the components and the services they
+have associated with them. Each TS file defines the behavior of the application component
+to which it corresponds, taking care of data processing and validations</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>MVVM</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.6268</v>
+        <v>0.8874</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M05_AU22</t>
+          <t>CF_M05_AU15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
-        </is>
-      </c>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
+          <t>Models are the TypeScript classes that define the data contract consumed by the
+view and the ViewModel. These classes allow the View to know what data to display and
+the ViewModel to know how to manipulate it</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
       <c r="H8" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.7126</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M05_AU23</t>
+          <t>CF_M05_AU16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
-        </is>
-      </c>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AU_11</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Communication Log</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0.7702</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU24</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>client(frontend), server (backend)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.7956</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M05_AU28</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
-structure and normalize communication with the data layer. </t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.6758999999999999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU32</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Server (Backend)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
-responsibilities are separated:</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0.7968</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CF_M05_P06</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Shared Database</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AU_05</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Data Access Layer</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7631</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0.9671</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0.9822</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>client(frontend), server (backend)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7956</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU27</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>viewmodel, view, model</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>MVVM</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.6965</v>
+        <v>0.8110000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CF_M05_AU28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
+structure and normalize communication with the data layer. </t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6758999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Server (Backend)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
+responsibilities are separated:</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.7968</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CF_M05_P06</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Shared Database</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>the microservices are connected to a shared database that is decoupled per
+microservice and client. There is a schema for each microservice and each client has its
+own set of schemas per microservice.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>AU_05</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Data Access Layer</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6893</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7027</v>
+        <v>0.75</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5652</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9167</v>
+        <v>0.9091</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6667</v>
+        <v>0.6061</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9085</v>
+        <v>0.9076</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8333</v>
+        <v>0.8182</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.75</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8335</v>
+        <v>0.8385</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2083</v>
+        <v>0.2273</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7059</v>
+        <v>0.6875</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -626,16 +626,16 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.8824</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6296</v>
+        <v>0.5556</v>
       </c>
     </row>
     <row r="3">
@@ -670,13 +670,13 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3077</v>
+        <v>0.4</v>
       </c>
       <c r="F4" t="n">
         <v>0.3077</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +756,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13 / 13</t>
+          <t>13 / 10</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7027</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5652</v>
+        <v>0.5217000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -888,22 +888,22 @@
         <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="n">
         <v>22</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F2" t="n">
-        <v>22</v>
-      </c>
-      <c r="G2" t="n">
-        <v>22</v>
-      </c>
-      <c r="H2" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -916,22 +916,22 @@
         <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -944,22 +944,22 @@
         <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -972,22 +972,22 @@
         <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G5" t="n">
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -1000,22 +1000,22 @@
         <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -1043,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1057,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1245,12 +1245,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M05_AU07</t>
+          <t>CF_M05_AU33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7569</v>
+        <v>0.7665</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kubernetes is a container orchestration platform used for deployment.</t>
+          <t>Kubernetes is a container orchestration platform used for deployment via Amazon EKS.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1283,19 +1283,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['AU_15']</t>
+          <t>['AU_14']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Amazon EKS</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1305,9 +1305,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
-which allows the use of Kubernetes (K8s), a container orchestration platform created by
-Google, without the need to install or maintain it. </t>
+          <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1315,13 +1313,13 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CF_M05_P05</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M05_AU07</t>
+          <t>CF_M05_AU33</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -1329,7 +1327,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1373,7 +1371,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1414,7 +1412,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1458,7 +1456,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1498,7 +1496,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1538,7 +1536,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1577,7 +1575,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1621,7 +1619,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1664,7 +1662,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1708,7 +1706,7 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1751,7 +1749,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1795,7 +1793,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1834,12 +1832,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M05_AU20</t>
+          <t>CF_M05_AU17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1848,11 +1846,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8441</v>
+        <v>0.9122</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Contract Layer</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1862,7 +1860,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>The contract layer separates the internal model from the external representation of the API.</t>
+          <t>The presentation layer receives requests and builds responses.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1878,13 +1876,13 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Contract Layer (DTO/Mappers)</t>
+          <t>Presentation Layer (Controllers)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1893,97 +1891,96 @@
         </is>
       </c>
       <c r="O10" t="inlineStr">
-        <is>
-          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
-request to be structured, providing a customized format based on response requirements.</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>73</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>CF_M05_P04</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU20</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AU_03</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.9122</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Presentation Layer</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>The presentation layer receives requests and builds responses.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>['P_05']</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>AU_03</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Presentation Layer (Controllers)</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
         <is>
           <t>The controllers, through specific
 functions, process the requests received, manage the validation of the information and channel
 the requests to the corresponding modules or services of the data layer.</t>
         </is>
       </c>
+      <c r="P10" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AU_05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9164</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Access Layer</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>The data access layer interacts with the database.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>['P_05']</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>AU_05</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Data access layer (Repositories)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>the Repositories are responsible for performing queries on the database.</t>
+        </is>
+      </c>
       <c r="P11" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1993,7 +1990,7 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M05_AU17</t>
+          <t>CF_M05_AU21</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -2001,12 +1998,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M05_AU21</t>
+          <t>CF_M05_AU19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2015,11 +2012,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9164</v>
+        <v>0.9445</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Access Layer</t>
+          <t>Domain Layer</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2029,7 +2026,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>The data access layer interacts with the database.</t>
+          <t>The domain layer defines the data model.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2045,13 +2042,13 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Data access layer (Repositories)</t>
+          <t>Domain Layer (Models)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2061,11 +2058,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>the Repositories are responsible for performing queries on the database.</t>
+          <t>Models represent the internal and persistent structure of the system entities, reflecting the
+stored information identically.</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2075,7 +2073,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M05_AU21</t>
+          <t>CF_M05_AU19</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2083,12 +2081,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M05_AU19</t>
+          <t>CF_M05_AU18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2097,11 +2095,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9445</v>
+        <v>0.9562</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Domain Layer</t>
+          <t>Business Logic Layer</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2111,7 +2109,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>The domain layer defines the data model.</t>
+          <t>The business logic layer applies the domain rules.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2127,13 +2125,13 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Domain Layer (Models)</t>
+          <t>Business Logic Layer (Services)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2143,12 +2141,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Models represent the internal and persistent structure of the system entities, reflecting the
-stored information identically.</t>
+          <t>Services provide the interface and implementation of all the application's business logic.</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2158,7 +2155,7 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M05_AU19</t>
+          <t>CF_M05_AU18</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2166,147 +2163,65 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M05_AU18</t>
+          <t>CF_M05_P04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.9562</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Business Logic Layer</t>
+          <t>Layered Architecture</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>The business logic layer applies the domain rules.</t>
+          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated: the presentation layer receives requests and builds responses, the business logic layer applies domain rules, the data access layer interacts with the database, and the domain layer defines the data model.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['P_05']</t>
+          <t>['P_03', 'AU_13']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Business Logic Layer (Services)</t>
+          <t>Layered Architecture</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
-        <is>
-          <t>Services provide the interface and implementation of all the application's business logic.</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>CF_M05_P04</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>CF_M05_AU18</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CF_M05_P04</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Layered Architecture</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated: the presentation layer receives requests and builds responses, the business logic layer applies domain rules, the data access layer interacts with the database, and the domain layer defines the data model.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>['P_03', 'AU_14']</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Layered Architecture</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
         <is>
           <t>Layered architecture is used: Spring Boot organizes the code following the pattern of layers with which
 responsibilities are separated: the presentation layer receives requests and constructs responses, the
@@ -2314,14 +2229,89 @@
 separates the internal model from the external representation of the API.</t>
         </is>
       </c>
+      <c r="P14" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CF_M05_P05</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Cloud Architecture</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>The application is designed, deployed, and executed using cloud services (cloud computing) instead of local or physical servers.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Cloud Architecture</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The application applies a cloud architecture . That is, the application is designed,
+deployed and executed using cloud services (cloud computing) instead of local or physical servers.</t>
+        </is>
+      </c>
       <c r="P15" t="n">
-        <v>68.69</v>
+        <v>60</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M05_P04</t>
+          <t>CF_M05_P05</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2329,17 +2319,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M05_P05</t>
+          <t>CF_M05_AU31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2347,17 +2337,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cloud Architecture</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>The application is designed, deployed, and executed using cloud services (cloud computing) instead of local or physical servers.</t>
+          <t>The message exchange protocol used in this case is HTTP.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2369,34 +2359,34 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Cloud Architecture</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The application applies a cloud architecture . That is, the application is designed,
-deployed and executed using cloud services (cloud computing) instead of local or physical servers.</t>
+          <t>The message
+exchange protocol used in this case is HTTP</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M05_P05</t>
+          <t>CF_M05_AU31</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2404,329 +2394,339 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M05_AU33</t>
+          <t>CF_M05_AU25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Docker</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Docker is used to create images for each microservice.</t>
+          <t>The client, which we also call frontEnd, is responsible for the presentation and user experience of the application, encapsulating the interface logic and the coordination of calls to the server's API.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>['AU_03', 'AU_04']</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Docker</t>
-        </is>
-      </c>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>presentation layer, business logic layer</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
+          <t>Data access and logic management in this project is carried out using REST operations, which structure and normalize communication with the data layer.</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
+          <t>CF_M05_AU17, CF_M05_AU21</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M05_AU33</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>CF_M05_AU25</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>presentation layer (controllers), data access layer (repositories)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
+          <t>CF_M05_AU26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>The exchange protocol used for communication between client and server.</t>
+          <t>The controllers, by means of specific functions, process the received requests, manage the validation of the information and channel the requests to the corresponding modules or services of the data layer.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>['AU_04', 'AU_05']</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>business logic layer, data access layer</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>The message
-exchange protocol used in this case is HTTP</t>
+          <t>This technology helps us in the communication between the data layer and the database of the project application.</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CF_M05_AU21, CF_M05_AU16</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>CF_M05_AU26</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>data access layer (repositories), database</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M05_AU25</t>
+          <t>CF_M05_AU29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Spring Boot</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The presentation layer (frontEnd) communicates with the server (backEnd) via HTTP.</t>
+          <t>Spring Boot is a framework that simplifies the creation of Java applications based on Spring, used for the backEnd.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_03', 'AU_04']</t>
+          <t>['AU_09', 'AU_10', 'AU_11', 'P_05']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>presentation layer, business logic layer</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Spring Boot</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Data access and logic management in this project is carried out using REST operations, which structure and normalize communication with the data layer.</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>69</v>
+          <t>Spring Boot is used, which provides a platform for exposing a REST API</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>61, 62</t>
+        </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M05_AU17, CF_M05_AU21</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M05_AU25</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>presentation layer (controllers), data access layer (repositories)</t>
-        </is>
-      </c>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M05_AU26</t>
+          <t>CF_M05_P03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MVVM</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>The business logic layer (Services) calls the corresponding functions to obtain the result of the request.</t>
+          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_05']</t>
+          <t>['P_03', 'AU_12']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_26</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>business logic layer, data access layer</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>MVVM</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>This technology helps us in the communication between the data layer and the database of the project application.</t>
+          <t xml:space="preserve">Angular applies the MVVM pattern (Model-View-ViewModel), since its architecture is
+based on components and services. </t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>CF_M05_AU21, CF_M05_AU16</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M05_AU26</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>data access layer (repositories), database</t>
-        </is>
-      </c>
+          <t>CF_M05_P03</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M05_AU29</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spring Boot</t>
+          <t>Angular</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Spring Boot is a framework used to accelerate the development of microservices and enterprise applications.</t>
+          <t>Angular is a web development framework created by Google, used for the frontEnd of the application.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2759,19 +2759,19 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['AU_08', 'AU_09', 'AU_10', 'AU_11', 'AU_12', 'P_05']</t>
+          <t>['AU_08', 'P_04']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Spring Boot</t>
+          <t>Angular</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2781,23 +2781,21 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Spring Boot is used, which provides a platform for exposing a REST API</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>61, 62</t>
-        </is>
+          <t>In the present project, the client has been developed with Angular</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>61</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
+          <t>CF_M05_AU06</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M05_AU29</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2805,12 +2803,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M05_P03</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2823,39 +2821,35 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MVVM</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
+          <t>The application has an architecture based on microservices, which consists of dividing the system into a set of small, independent, and autonomous services where each microservice is responsible for a specific functionality.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>['P_03', 'AU_13']</t>
-        </is>
-      </c>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>MVVM</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2865,18 +2859,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Angular applies the MVVM pattern (Model-View-ViewModel), since its architecture is
-based on components and services. </t>
+          <t>Application has an architecture based on microservices.</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CF_M05_P03</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2884,17 +2877,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2902,220 +2895,64 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Angular</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Angular is a web development framework used for the frontEnd of the application.</t>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>['AU_09', 'P_04']</t>
-        </is>
-      </c>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Angular</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
-        <is>
-          <t>In the present project, the client has been developed with Angular</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>CF_M05_AU06</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>CF_M05_AU30</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CF_M05_P01</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>The application has an architecture based on microservices, which consists of dividing the system into a set of small, independent, and autonomous services where each microservice is responsible for a specific functionality.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Application has an architecture based on microservices.</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>CF_M05_P01</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CF_M05_P02</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
         <is>
           <t>The application follows the Client-Server pattern which organizes the code into two distinct
 components: the client, which makes service requests, and the server, which receives,
 processes, and returns responses.</t>
         </is>
       </c>
-      <c r="P25" t="n">
+      <c r="P23" t="n">
         <v>61</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
         <is>
           <t>Classification Changed</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3128,7 +2965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3192,7 +3029,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The administrator is a user with additional permissions to manage application access for users.</t>
+          <t>The administrator is a user with additional permissions to manage application access.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3212,7 +3049,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3228,7 +3065,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The data format used for communication.</t>
+          <t>The data format used is JSON.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3248,7 +3085,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3280,7 +3117,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3291,32 +3128,28 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>portal, leader, access control, communication log, scheduler</t>
+          <t>portal, leader</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The portal microservice has as its main function to offer a centralized interface for access to the different VWGS applications. [...] This component acts as an entry point for users, providing a unified experience.</t>
+          <t>The portal microservice has as its main function to offer a centralized interface for access to the different VWGS applications. [...] In each portal, the relevant authentication and authorization controls are carried out with the help of the Leader which decides to which functional domain each user should be routed.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M05_AU02</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Portal Microservice</t>
-        </is>
-      </c>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3359,32 +3192,32 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>user, portal</t>
+          <t>business logic layer, data access layer</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The user accesses the portal and applications.</t>
+          <t>The services offer the interface and the implementation of all the business logic of the application. [...] these call the corresponding functions to obtain the result of the request.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M05_AU02</t>
+          <t>CF_M05_AU18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Portal Microservice</t>
+          <t>Business Logic Layer (Services)</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.7501</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3395,62 +3228,26 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>presentation layer, business logic layer</t>
+          <t>data access layer, domain layer</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The presentation layer (Controllers) processes the requests received, manages the validation of the information and channels the requests to the corresponding modules or services of the data layer.</t>
+          <t>Finally, the Repositories are in charge of performing queries on the database.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M05_AU17</t>
+          <t>CF_M05_AU21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Presentation Layer (Controllers)</t>
+          <t>Data access layer (Repositories)</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8548</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>data access layer, domain layer</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>The data access layer (Repositories) is responsible for performing queries on the database.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CF_M05_AU21</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Data access layer (Repositories)</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0.9316</v>
+        <v>0.7919</v>
       </c>
     </row>
   </sheetData>
@@ -3464,7 +3261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3535,22 +3332,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.8405</v>
+        <v>0.8626</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AU08</t>
+          <t>CF_M05_AU07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3560,11 +3353,49 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SonarQube</t>
+          <t>Amazon EKS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
+which allows the use of Kubernetes (K8s), a container orchestration platform created by
+Google, without the need to install or maintain it. </t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Amazon Web Services</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7812</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CF_M05_AU08</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SonarQube</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
         <is>
           <t>SonarQube is a
 web application that statically analyses the code and offers recommendations and statistics
@@ -3572,312 +3403,285 @@
 problems, the amount of code covered in the tests, code duplication and code smells.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Kubernetes</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H4" t="n">
         <v>0.6439</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CF_M05_AU09</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Grafana</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Kubernetes</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0.6829</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AU11</t>
+          <t>CF_M05_AU09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Grafana</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Kubernetes</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6829</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CF_M05_AU11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ordering</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>These two microservices are responsible for
 calls to external services related to car sales.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H6" t="n">
         <v>0.6729000000000001</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>CF_M05_AU12</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>GSB</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
         <is>
           <t>These two microservices are responsible for
 calls to external services related to car sales.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Leader</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>0.6268</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>CF_M05_AU14</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>ViewModel</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
         <is>
           <t>The ViewModel component groups the TS files of the components and the services they
 have associated with them. Each TS file defines the behavior of the application component
 to which it corresponds, taking care of data processing and validations</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>MVVM</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H8" t="n">
         <v>0.8874</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>CF_M05_AU15</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Models are the TypeScript classes that define the data contract consumed by the
 view and the ViewModel. These classes allow the View to know what data to display and
 the ViewModel to know how to manipulate it</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H9" t="n">
         <v>0.7126</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>CF_M05_AU16</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Database</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Data Access Layer</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H10" t="n">
         <v>0.7631</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>0.9671</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M05_AU23</t>
+          <t>CF_M05_AU20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
-        </is>
-      </c>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Contract Layer (DTO/Mappers)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
+          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
+request to be structured, providing a customized format based on response requirements.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Business Logic Layer</t>
+        </is>
+      </c>
       <c r="H11" t="n">
-        <v>0.9822</v>
+        <v>0.7371</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M05_AU24</t>
+          <t>CF_M05_AU22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3888,32 +3692,28 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>client(frontend), server (backend)</t>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
+          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.7956</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CF_M05_AU27</t>
+          <t>CF_M05_AU23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3924,137 +3724,205 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>viewmodel, view, model</t>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MVVM</t>
-        </is>
-      </c>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.9822</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>CF_M05_AU24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>client(frontend), server (backend)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7956</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CF_M05_AU27</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>viewmodel, view, model</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MVVM</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>CF_M05_AU28</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>REST</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
         <is>
           <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
 structure and normalize communication with the data layer. </t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="H16" t="n">
         <v>0.6758999999999999</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Server (Backend)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
 responsibilities are separated:</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="H17" t="n">
         <v>0.7968</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>CF_M05_P06</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Design Pattern</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Shared Database</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Data Access Layer</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="H18" t="n">
         <v>0.6893</v>
       </c>
     </row>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.75</v>
+        <v>0.7188</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9091</v>
+        <v>0.7308</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6061</v>
+        <v>0.5758</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9076</v>
+        <v>0.9297</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8182</v>
+        <v>0.85</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8385</v>
+        <v>0.8574000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2273</v>
+        <v>0.55</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fixes</t>
+          <t>fixedType</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -626,16 +626,16 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8824</v>
+        <v>0.6667</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5556</v>
+        <v>0.5185</v>
       </c>
     </row>
     <row r="3">
@@ -670,13 +670,13 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4</v>
+        <v>0.6667</v>
       </c>
       <c r="F4" t="n">
         <v>0.3077</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +756,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13 / 10</t>
+          <t>13 / 6</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.75</v>
+        <v>0.7188</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
@@ -888,22 +888,22 @@
         <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" t="n">
         <v>20</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H2" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -916,22 +916,22 @@
         <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -944,22 +944,22 @@
         <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
         <v>16</v>
       </c>
       <c r="H4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -972,22 +972,22 @@
         <v>38</v>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -1000,28 +1000,28 @@
         <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fixes</t>
+          <t>fixedType</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1043,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1057,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T23"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>LLM_fixes</t>
+          <t>LLM_fixedType</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>GT_fixes</t>
+          <t>GT_fixedType</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
@@ -1165,12 +1165,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M05_AU13</t>
+          <t>CF_M05_AU02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1179,213 +1179,51 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7551</v>
+        <v>0.785</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The user is the actor who accesses the portal and applications.</t>
+          <t>The portal microservice has as its main function to offer a centralized interface for access to the different VWGS applications.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>['P_01']</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Portal Microservice</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
-        <is>
-          <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
-each component that makes up the application. They are responsible for presenting the
-screens and capturing user interactions such as clicks or text entries.</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>CF_M05_P03</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>CF_M05_AU13</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CF_M05_AU33</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0.7665</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Kubernetes</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Kubernetes is a container orchestration platform used for deployment via Amazon EKS.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>['AU_14']</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Docker</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>CF_M05_AU32</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>CF_M05_AU33</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CF_M05_AU02</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>The portal microservice has as its main function to offer a centralized interface for access to the different VWGS applications.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>['P_01']</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Portal Microservice</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">The portal microservice's main function is to provide a centralized interface for accessing the different VWGS
 applications. This component acts as an entry point for users, providing a unified experience. In addition to its
@@ -1393,247 +1231,168 @@
 itself and the rest of the portal's applications. </t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="P2" t="n">
         <v>57</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="T2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>CF_M05_AU01</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D3" t="n">
         <v>0.7874</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Leader</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>This microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Leader Microservice</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>This microservice has as its main function the routing of all communications to the corresponding microservice
 within the system architecture. It acts as a central point for traffic management, ensuring that any interaction,
 both with external services and between internal microservices, is carried out in an orderly and secure manner.</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="P3" t="n">
         <v>57</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>CF_M05_AU01</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CF_M05_AU10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="T3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CF_M05_AU05</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>0.8105</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Amazon Web Services</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>The provider for this project is Amazon Web Services which has a wide catalog of cloud services and resources.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="D4" t="n">
+        <v>0.8361</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Scheduler</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>This microservice has as its main function the planning and programming of processes within the system.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Amazon RDS</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
-microservice and client. </t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>CF_M05_P05</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>CF_M05_AU10</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AU_11</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU05</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.8361</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Scheduler</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>['P_01']</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Scheduler Microservice</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>This microservice has as its main function the planning and programming of processes within the system.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>['P_01']</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>AU_11</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Scheduler Microservice</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Its main function is the
 planning and scheduling of processes within the system. This component allows you to define,
@@ -1643,84 +1402,84 @@
 microservices.</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="P4" t="n">
         <v>59.6</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>CF_M05_AU05</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="T4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D5" t="n">
         <v>0.8378</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Communication Log</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>The Communication Log microservice has as its main purpose to record all communications that occur within the system.</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Communication Log Microservice</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>The main purpose of the Communication Log microservice is to record all
 communications that occur within the system, both between microservices and with external
@@ -1730,175 +1489,419 @@
 and faster analysis.</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="P5" t="n">
         <v>58.59</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="T5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>CF_M05_AU03</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D6" t="n">
         <v>0.8439</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Access Control</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>The Access Control microservice has as its main objective the management of user authentication and their permissions within the application.</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Access Control Microservice</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t xml:space="preserve">The main objective of the Access Control microservice is to manage user authentication and
 permissions within the application. </t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="P6" t="n">
         <v>58</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>CF_M05_AU03</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="T6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CF_M05_AU20</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8441</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Contract Layer</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>The contract layer separates the internal model from the external representation of the API.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Contract Layer (DTO/Mappers)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
+request to be structured, providing a customized format based on response requirements.</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>CF_M05_AU20</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>CF_M05_AU17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D8" t="n">
         <v>0.9122</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Presentation Layer</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>The presentation layer receives requests and builds responses.</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>['P_05']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Presentation Layer (Controllers)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>The controllers, through specific
 functions, process the requests received, manage the validation of the information and channel
 the requests to the corresponding modules or services of the data layer.</t>
         </is>
       </c>
+      <c r="P8" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AU_05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU21</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9164</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Access Layer</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>The data access layer interacts with the database.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>['P_05']</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>AU_05</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Data access layer (Repositories)</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>the Repositories are responsible for performing queries on the database.</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU21</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AU_06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU19</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9445</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Domain Layer</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>The domain layer defines the data model.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>['P_05']</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>AU_06</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Domain Layer (Models)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Models represent the internal and persistent structure of the system entities, reflecting the
+stored information identically.</t>
+        </is>
+      </c>
       <c r="P10" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1908,7 +1911,7 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M05_AU17</t>
+          <t>CF_M05_AU19</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1916,12 +1919,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M05_AU21</t>
+          <t>CF_M05_AU18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1930,11 +1933,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9164</v>
+        <v>0.9562</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Access Layer</t>
+          <t>Business Logic Layer</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1944,12 +1947,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>The data access layer interacts with the database.</t>
+          <t>The business logic layer applies the domain rules.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1960,13 +1963,13 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Data access layer (Repositories)</t>
+          <t>Business Logic Layer (Services)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1976,11 +1979,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>the Repositories are responsible for performing queries on the database.</t>
+          <t>Services provide the interface and implementation of all the application's business logic.</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1990,7 +1993,7 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M05_AU21</t>
+          <t>CF_M05_AU18</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1998,230 +2001,65 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M05_AU19</t>
+          <t>CF_M05_P04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9445</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Domain Layer</t>
+          <t>Layered Architecture</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>The domain layer defines the data model.</t>
+          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated: the presentation layer receives requests and builds responses, the business logic layer applies domain rules, the data access layer interacts with the database, and the domain layer defines the data model.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['P_05']</t>
+          <t>['P_03', 'AU_14']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Domain Layer (Models)</t>
+          <t>Layered Architecture</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
-        <is>
-          <t>Models represent the internal and persistent structure of the system entities, reflecting the
-stored information identically.</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>CF_M05_P04</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU19</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CF_M05_AU18</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.9562</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Business Logic Layer</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>The business logic layer applies the domain rules.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>['P_05']</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Business Logic Layer (Services)</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Services provide the interface and implementation of all the application's business logic.</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>CF_M05_P04</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>CF_M05_AU18</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CF_M05_P04</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Layered Architecture</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated: the presentation layer receives requests and builds responses, the business logic layer applies domain rules, the data access layer interacts with the database, and the domain layer defines the data model.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>['P_03', 'AU_13']</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Layered Architecture</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
         <is>
           <t>Layered architecture is used: Spring Boot organizes the code following the pattern of layers with which
 responsibilities are separated: the presentation layer receives requests and constructs responses, the
@@ -2229,14 +2067,172 @@
 separates the internal model from the external representation of the API.</t>
         </is>
       </c>
+      <c r="P12" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU28</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Spring Boot, which provides a platform for exposing a REST API.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>['AU_23']</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
+structure and normalize communication with the data layer. </t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17, CF_M05_AU21</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU28</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CF_M05_P05</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Cloud Architecture</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>The application is designed, deployed, and executed using cloud services (cloud computing) instead of local or physical servers.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Cloud Architecture</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> The application applies a cloud architecture . That is, the application is designed,
+deployed and executed using cloud services (cloud computing) instead of local or physical servers.</t>
+        </is>
+      </c>
       <c r="P14" t="n">
-        <v>68.69</v>
+        <v>60</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M05_P04</t>
+          <t>CF_M05_P05</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2244,17 +2240,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M05_P05</t>
+          <t>CF_M05_AU31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2262,56 +2258,60 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cloud Architecture</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>The application is designed, deployed, and executed using cloud services (cloud computing) instead of local or physical servers.</t>
+          <t>The message exchange protocol used in this case is HTTP.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>['AU_14', 'AU_23']</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Cloud Architecture</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The application applies a cloud architecture . That is, the application is designed,
-deployed and executed using cloud services (cloud computing) instead of local or physical servers.</t>
+          <t>The message
+exchange protocol used in this case is HTTP</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M05_P05</t>
+          <t>CF_M05_AU31</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2319,251 +2319,257 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
+          <t>CF_M05_AU24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>The message exchange protocol used in this case is HTTP.</t>
+          <t>The client, which we also call frontEnd, is responsible for the presentation and user experience of the application. [...] The ViewModel acts as an intermediary between the View and the Model, providing the data that the view needs and managing the user's actions.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>61,64</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>['AU_13', 'AU_14']</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>frontend, backend</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>The message
-exchange protocol used in this case is HTTP</t>
+          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CF_M05_AU06, CF_M05_AU32</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>CF_M05_AU24</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>client(frontend), server (backend)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M05_AU25</t>
+          <t>CF_M05_AU29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Spring Boot</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>The client, which we also call frontEnd, is responsible for the presentation and user experience of the application, encapsulating the interface logic and the coordination of calls to the server's API.</t>
+          <t>Spring Boot is a framework that simplifies the creation of Java-based applications, used for the backEnd.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['AU_03', 'AU_04']</t>
+          <t>['AU_14', 'P_05']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>presentation layer, business logic layer</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Spring Boot</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Data access and logic management in this project is carried out using REST operations, which structure and normalize communication with the data layer.</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>69</v>
+          <t>Spring Boot is used, which provides a platform for exposing a REST API</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>61, 62</t>
+        </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M05_AU17, CF_M05_AU21</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M05_AU25</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>presentation layer (controllers), data access layer (repositories)</t>
-        </is>
-      </c>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M05_AU26</t>
+          <t>CF_M05_P03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MVVM</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>The controllers, by means of specific functions, process the received requests, manage the validation of the information and channel the requests to the corresponding modules or services of the data layer.</t>
+          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_04', 'AU_05']</t>
+          <t>['P_03', 'AU_13']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>business logic layer, data access layer</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>MVVM</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>This technology helps us in the communication between the data layer and the database of the project application.</t>
+          <t xml:space="preserve">Angular applies the MVVM pattern (Model-View-ViewModel), since its architecture is
+based on components and services. </t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>CF_M05_AU21, CF_M05_AU16</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M05_AU26</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>data access layer (repositories), database</t>
-        </is>
-      </c>
+          <t>CF_M05_P03</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M05_AU29</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2576,7 +2582,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spring Boot</t>
+          <t>Angular</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2586,29 +2592,29 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Spring Boot is a framework that simplifies the creation of Java applications based on Spring, used for the backEnd.</t>
+          <t>Angular is a web development framework created by Google, used for the frontEnd.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_09', 'AU_10', 'AU_11', 'P_05']</t>
+          <t>['AU_13', 'P_04']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Spring Boot</t>
+          <t>Angular</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2618,23 +2624,21 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Spring Boot is used, which provides a platform for exposing a REST API</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>61, 62</t>
-        </is>
+          <t>In the present project, the client has been developed with Angular</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>61</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
+          <t>CF_M05_AU06</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M05_AU29</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2642,12 +2646,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M05_P03</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2660,39 +2664,35 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MVVM</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
+          <t>The application has an architecture based on microservices, which consists of dividing the system into a set of small, independent, and autonomous services where each microservice is responsible for a specific functionality.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>['P_03', 'AU_12']</t>
-        </is>
-      </c>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MVVM</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2702,18 +2702,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Angular applies the MVVM pattern (Model-View-ViewModel), since its architecture is
-based on components and services. </t>
+          <t>Application has an architecture based on microservices.</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M05_P03</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2721,17 +2720,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2739,220 +2738,64 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Angular</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Angular is a web development framework created by Google, used for the frontEnd of the application.</t>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>['AU_08', 'P_04']</t>
-        </is>
-      </c>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Angular</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
-        <is>
-          <t>In the present project, the client has been developed with Angular</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>CF_M05_AU06</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>CF_M05_AU30</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CF_M05_P01</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>The application has an architecture based on microservices, which consists of dividing the system into a set of small, independent, and autonomous services where each microservice is responsible for a specific functionality.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Application has an architecture based on microservices.</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>CF_M05_P01</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CF_M05_P02</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
         <is>
           <t>The application follows the Client-Server pattern which organizes the code into two distinct
 components: the client, which makes service requests, and the server, which receives,
 processes, and returns responses.</t>
         </is>
       </c>
-      <c r="P23" t="n">
+      <c r="P21" t="n">
         <v>61</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Classification Changed</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2965,7 +2808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3013,7 +2856,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3023,231 +2866,343 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>User</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The administrator is a user with additional permissions to manage application access.</t>
+          <t>The user is the actor who accesses the portal and applications.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
+          <t>CF_M05_AU13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Server (Backend)</t>
+          <t>View</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.6979</v>
+        <v>0.7551</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The data format used is JSON.</t>
+          <t>The administrator is a user with additional permissions to assign or revoke access to applications.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Server (Backend)</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.678</v>
+        <v>0.6979</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>leader, portal, access control, communication log, scheduler</t>
-        </is>
-      </c>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The Leader microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
+          <t>The client, which we also call frontEnd, is responsible for the presentation and user experience of the application.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>CF_M05_AU06</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Client(Frontend)</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>0.9671</v>
+        <v>0.8573</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>portal, leader</t>
-        </is>
-      </c>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The portal microservice has as its main function to offer a centralized interface for access to the different VWGS applications. [...] In each portal, the relevant authentication and authorization controls are carried out with the help of the Leader which decides to which functional domain each user should be routed.</t>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the layered pattern.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Server (Backend)</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>0.825</v>
+        <v>0.9097</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>communication log, leader, portal, access control, scheduler</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The Communication Log microservice has as its main purpose to record all communications that occur within the system, both between microservices and with external services.</t>
+          <t>The data format used is JSON.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M05_AU23</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>CF_M05_AU31</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>0.9822</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>business logic layer, data access layer</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Amazon Web Services</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The services offer the interface and the implementation of all the business logic of the application. [...] these call the corresponding functions to obtain the result of the request.</t>
+          <t>The provider for this project is Amazon Web Services.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M05_AU18</t>
+          <t>CF_M05_AU10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Business Logic Layer (Services)</t>
+          <t>Amazon RDS</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8105</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Kubernetes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Kubernetes is a container orchestration platform used for deployment.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU33</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Docker</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7665</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>leader, portal, access control, communication log, scheduler</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>The Leader microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0.9671</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>frontend, backend</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>The communication between the two components [client and server] is done through an exchange of messages following standard network protocols and using interoperable data representation formats.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU24</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Connector</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>data access layer, domain layer</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Finally, the Repositories are in charge of performing queries on the database.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data access layer, backend</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>The data access layer interacts with the database.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>CF_M05_AU21</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Data access layer (Repositories)</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>0.7919</v>
+      <c r="H11" t="n">
+        <v>0.8915</v>
       </c>
     </row>
   </sheetData>
@@ -3261,7 +3216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3332,12 +3287,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
       <c r="H2" t="n">
-        <v>0.8626</v>
+        <v>0.8573</v>
       </c>
     </row>
     <row r="3">
@@ -3366,7 +3325,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3405,7 +3364,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3441,7 +3400,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3456,264 +3415,266 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AU11</t>
+          <t>CF_M05_AU10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Amazon RDS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
+          <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
+microservice and client. </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Amazon Web Services</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8105</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CF_M05_AU11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ordering</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>These two microservices are responsible for
 calls to external services related to car sales.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>0.6729000000000001</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>CF_M05_AU12</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>GSB</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
         <is>
           <t>These two microservices are responsible for
 calls to external services related to car sales.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Leader</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H8" t="n">
         <v>0.6268</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
+each component that makes up the application. They are responsible for presenting the
+screens and capturing user interactions such as clicks or text entries.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7551</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>CF_M05_AU14</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>ViewModel</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
         <is>
           <t>The ViewModel component groups the TS files of the components and the services they
 have associated with them. Each TS file defines the behavior of the application component
 to which it corresponds, taking care of data processing and validations</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>MVVM</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H10" t="n">
         <v>0.8874</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>CF_M05_AU15</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Models are the TypeScript classes that define the data contract consumed by the
 view and the ViewModel. These classes allow the View to know what data to display and
 the ViewModel to know how to manipulate it</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>0.7126</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>CF_M05_AU16</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Database</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Data Access Layer</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.7631</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M05_AU20</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Contract Layer (DTO/Mappers)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
-request to be structured, providing a customized format based on response requirements.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Business Logic Layer</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.7371</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.9671</v>
+        <v>0.7869</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CF_M05_AU23</t>
+          <t>CF_M05_AU22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3724,28 +3685,28 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
+          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.9822</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CF_M05_AU24</t>
+          <t>CF_M05_AU23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3756,32 +3717,32 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>client(frontend), server (backend)</t>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
+          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Communication Log</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.7956</v>
+        <v>0.7702</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CF_M05_AU27</t>
+          <t>CF_M05_AU25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3792,138 +3753,193 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>viewmodel, view, model</t>
+          <t>presentation layer (controllers), data access layer (repositories)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+          <t>Data access and logic management in this project is carried out using REST operations, which structure and normalize communication with the data layer.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MVVM</t>
-        </is>
-      </c>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.7479</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CF_M05_AU28</t>
+          <t>CF_M05_AU26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>data access layer (repositories), database</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
-structure and normalize communication with the data layer. </t>
+          <t>This technology helps us in the communication between the data layer and the database of the project application.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.8274</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>CF_M05_AU27</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>viewmodel, view, model</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0.8557</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Server (Backend)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
 responsibilities are separated:</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>0.7968</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9097</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CF_M05_AU33</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Docker</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Kubernetes</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0.7665</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>CF_M05_P06</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Design Pattern</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Shared Database</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Data Access Layer</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>0.6893</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0.7251</v>
       </c>
     </row>
   </sheetData>
